--- a/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_PCL_PROPORSI USAHA.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_PCL_PROPORSI USAHA.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,202 +417,202 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Nama PCL</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Email PCL</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Nama PML</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Email PML</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>nama_kec</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>koseka</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Jumlah Usaha Berhasil Didata (semua status keberadaan usaha)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Jumlah Usaha Didata</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Persentase Usaha Didata</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Jumlah Usaha dalam Keluarga Didata</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Persentase Usaha dalam Keluarga Didata</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>DRAFT</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>APPROVED BY Pengawas</t>
         </is>
@@ -677,13 +665,13 @@
         <v>227.32</v>
       </c>
       <c r="L2" t="n">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="M2" t="n">
-        <v>260</v>
+        <v>302</v>
       </c>
       <c r="N2" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="O2" t="n">
         <v>3</v>
@@ -692,7 +680,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -701,31 +689,31 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>36</v>
+        <v>89</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>472</v>
+        <v>499</v>
       </c>
       <c r="W2" t="n">
-        <v>343</v>
+        <v>393</v>
       </c>
       <c r="X2" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="Y2" t="n">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="Z2" t="n">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="AA2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AB2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -737,16 +725,16 @@
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>36</v>
+        <v>89</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>489</v>
+        <v>499</v>
       </c>
       <c r="AI2" t="n">
-        <v>374</v>
+        <v>393</v>
       </c>
       <c r="AJ2" t="n">
         <v>364</v>
@@ -945,10 +933,10 @@
         <v>233.54</v>
       </c>
       <c r="L4" t="n">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="M4" t="n">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -957,7 +945,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -969,7 +957,7 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -978,13 +966,13 @@
         <v>429</v>
       </c>
       <c r="W4" t="n">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="X4" t="n">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="Y4" t="n">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
@@ -993,7 +981,7 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1005,7 +993,7 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
@@ -1014,7 +1002,7 @@
         <v>429</v>
       </c>
       <c r="AI4" t="n">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="AJ4" t="n">
         <v>363</v>
@@ -1082,7 +1070,7 @@
         <v>219</v>
       </c>
       <c r="M5" t="n">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -1103,10 +1091,10 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>425</v>
@@ -1118,7 +1106,7 @@
         <v>219</v>
       </c>
       <c r="Y5" t="n">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
@@ -1139,10 +1127,10 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH5" t="n">
         <v>425</v>
@@ -1213,16 +1201,16 @@
         <v>133.34</v>
       </c>
       <c r="L6" t="n">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="M6" t="n">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -1237,28 +1225,28 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="W6" t="n">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="X6" t="n">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="Y6" t="n">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -1273,16 +1261,16 @@
         <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AI6" t="n">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="AJ6" t="n">
         <v>354</v>
@@ -1347,13 +1335,13 @@
         <v>342.14</v>
       </c>
       <c r="L7" t="n">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="M7" t="n">
-        <v>253</v>
+        <v>275</v>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1377,19 +1365,19 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="W7" t="n">
-        <v>303</v>
+        <v>323</v>
       </c>
       <c r="X7" t="n">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="Y7" t="n">
-        <v>253</v>
+        <v>275</v>
       </c>
       <c r="Z7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1413,10 +1401,10 @@
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AI7" t="n">
-        <v>303</v>
+        <v>323</v>
       </c>
       <c r="AJ7" t="n">
         <v>336</v>
@@ -1481,16 +1469,16 @@
         <v>473.49</v>
       </c>
       <c r="L8" t="n">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="M8" t="n">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="O8" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1511,22 +1499,22 @@
         <v>1</v>
       </c>
       <c r="V8" t="n">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="W8" t="n">
-        <v>213</v>
+        <v>234</v>
       </c>
       <c r="X8" t="n">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="Y8" t="n">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="Z8" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="AA8" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -1547,10 +1535,10 @@
         <v>1</v>
       </c>
       <c r="AH8" t="n">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="AI8" t="n">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="AJ8" t="n">
         <v>304</v>
@@ -1615,13 +1603,13 @@
         <v>437.67</v>
       </c>
       <c r="L9" t="n">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="M9" t="n">
-        <v>256</v>
+        <v>275</v>
       </c>
       <c r="N9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1645,19 +1633,19 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="W9" t="n">
-        <v>306</v>
+        <v>326</v>
       </c>
       <c r="X9" t="n">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="Y9" t="n">
-        <v>256</v>
+        <v>275</v>
       </c>
       <c r="Z9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1681,10 +1669,10 @@
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AI9" t="n">
-        <v>306</v>
+        <v>326</v>
       </c>
       <c r="AJ9" t="n">
         <v>288</v>
@@ -1752,16 +1740,16 @@
         <v>186</v>
       </c>
       <c r="M10" t="n">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="N10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>7</v>
       </c>
       <c r="P10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -1788,16 +1776,16 @@
         <v>186</v>
       </c>
       <c r="Y10" t="n">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="Z10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
         <v>7</v>
       </c>
       <c r="AB10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1883,19 +1871,19 @@
         <v>207.78</v>
       </c>
       <c r="L11" t="n">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="M11" t="n">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1907,31 +1895,31 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
         <v>407</v>
       </c>
       <c r="W11" t="n">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="X11" t="n">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="Y11" t="n">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="Z11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1943,16 +1931,16 @@
         <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="AG11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
         <v>407</v>
       </c>
       <c r="AI11" t="n">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="AJ11" t="n">
         <v>373</v>
@@ -2017,13 +2005,13 @@
         <v>269.98</v>
       </c>
       <c r="L12" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="M12" t="n">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="N12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -2041,25 +2029,25 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="W12" t="n">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="X12" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="Y12" t="n">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="Z12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
         <v>1</v>
@@ -2077,16 +2065,16 @@
         <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="AI12" t="n">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="AJ12" t="n">
         <v>383</v>
@@ -2151,13 +2139,13 @@
         <v>325.91</v>
       </c>
       <c r="L13" t="n">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="M13" t="n">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="N13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2181,19 +2169,19 @@
         <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="W13" t="n">
-        <v>366</v>
+        <v>382</v>
       </c>
       <c r="X13" t="n">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="Y13" t="n">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="Z13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2217,10 +2205,10 @@
         <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="AI13" t="n">
-        <v>366</v>
+        <v>382</v>
       </c>
       <c r="AJ13" t="n">
         <v>373</v>
@@ -2285,16 +2273,16 @@
         <v>224.73</v>
       </c>
       <c r="L14" t="n">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="M14" t="n">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="N14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O14" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -2318,19 +2306,19 @@
         <v>426</v>
       </c>
       <c r="W14" t="n">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="X14" t="n">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="Y14" t="n">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="Z14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AA14" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -2354,7 +2342,7 @@
         <v>426</v>
       </c>
       <c r="AI14" t="n">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="AJ14" t="n">
         <v>364</v>
@@ -2419,13 +2407,13 @@
         <v>267.79</v>
       </c>
       <c r="L15" t="n">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="M15" t="n">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="N15" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="O15" t="n">
         <v>1</v>
@@ -2443,25 +2431,25 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="W15" t="n">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="X15" t="n">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="Y15" t="n">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="Z15" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AA15" t="n">
         <v>1</v>
@@ -2479,16 +2467,16 @@
         <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AI15" t="n">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="AJ15" t="n">
         <v>324</v>
@@ -2553,13 +2541,13 @@
         <v>60.62</v>
       </c>
       <c r="L16" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="M16" t="n">
-        <v>236</v>
+        <v>257</v>
       </c>
       <c r="N16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2568,7 +2556,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2580,22 +2568,22 @@
         <v>30</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" t="n">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="W16" t="n">
-        <v>273</v>
+        <v>295</v>
       </c>
       <c r="X16" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="Y16" t="n">
-        <v>236</v>
+        <v>257</v>
       </c>
       <c r="Z16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2604,7 +2592,7 @@
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2616,13 +2604,13 @@
         <v>30</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH16" t="n">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="AI16" t="n">
-        <v>273</v>
+        <v>295</v>
       </c>
       <c r="AJ16" t="n">
         <v>288</v>
@@ -2687,25 +2675,25 @@
         <v>197.73</v>
       </c>
       <c r="L17" t="n">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="M17" t="n">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="P17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -2717,31 +2705,31 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="W17" t="n">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="X17" t="n">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="Y17" t="n">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="Z17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AA17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AB17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2753,10 +2741,10 @@
         <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="AI17" t="n">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="AJ17" t="n">
         <v>370</v>
@@ -2821,19 +2809,19 @@
         <v>278.57</v>
       </c>
       <c r="L18" t="n">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="M18" t="n">
-        <v>199</v>
+        <v>225</v>
       </c>
       <c r="N18" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="O18" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="P18" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -2851,25 +2839,25 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="W18" t="n">
-        <v>311</v>
+        <v>350</v>
       </c>
       <c r="X18" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="Y18" t="n">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="Z18" t="n">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="AA18" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AB18" t="n">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2887,10 +2875,10 @@
         <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AI18" t="n">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="AJ18" t="n">
         <v>366</v>
@@ -2955,13 +2943,13 @@
         <v>220.8</v>
       </c>
       <c r="L19" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="M19" t="n">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="N19" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2988,16 +2976,16 @@
         <v>454</v>
       </c>
       <c r="W19" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="X19" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Y19" t="n">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="Z19" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -3024,7 +3012,7 @@
         <v>454</v>
       </c>
       <c r="AI19" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AJ19" t="n">
         <v>423</v>
@@ -3226,10 +3214,10 @@
         <v>186</v>
       </c>
       <c r="M21" t="n">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>2</v>
@@ -3247,7 +3235,7 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -3262,10 +3250,10 @@
         <v>186</v>
       </c>
       <c r="Y21" t="n">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="Z21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
         <v>2</v>
@@ -3283,7 +3271,7 @@
         <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -3357,16 +3345,16 @@
         <v>172.34</v>
       </c>
       <c r="L22" t="n">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="M22" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O22" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="P22" t="n">
         <v>7</v>
@@ -3387,22 +3375,22 @@
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="W22" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="X22" t="n">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="Y22" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA22" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="AB22" t="n">
         <v>7</v>
@@ -3423,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AI22" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AJ22" t="n">
         <v>410</v>
@@ -3491,19 +3479,19 @@
         <v>200.2</v>
       </c>
       <c r="L23" t="n">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="M23" t="n">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -3521,25 +3509,25 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="W23" t="n">
+        <v>313</v>
+      </c>
+      <c r="X23" t="n">
+        <v>220</v>
+      </c>
+      <c r="Y23" t="n">
         <v>296</v>
       </c>
-      <c r="X23" t="n">
-        <v>236</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>286</v>
-      </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3557,10 +3545,10 @@
         <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AI23" t="n">
-        <v>296</v>
+        <v>313</v>
       </c>
       <c r="AJ23" t="n">
         <v>450</v>
@@ -3625,22 +3613,22 @@
         <v>237.58</v>
       </c>
       <c r="L24" t="n">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="M24" t="n">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="N24" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="O24" t="n">
         <v>1</v>
       </c>
       <c r="P24" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="Q24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3649,7 +3637,7 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -3658,25 +3646,25 @@
         <v>402</v>
       </c>
       <c r="W24" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="X24" t="n">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="Y24" t="n">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="Z24" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="AA24" t="n">
         <v>1</v>
       </c>
       <c r="AB24" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="AC24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
@@ -3685,7 +3673,7 @@
         <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -3694,7 +3682,7 @@
         <v>402</v>
       </c>
       <c r="AI24" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AJ24" t="n">
         <v>359</v>
@@ -3759,13 +3747,13 @@
         <v>318.53</v>
       </c>
       <c r="L25" t="n">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="M25" t="n">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3789,19 +3777,19 @@
         <v>1</v>
       </c>
       <c r="V25" t="n">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="W25" t="n">
-        <v>277</v>
+        <v>298</v>
       </c>
       <c r="X25" t="n">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="Y25" t="n">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3825,10 +3813,10 @@
         <v>1</v>
       </c>
       <c r="AH25" t="n">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="AI25" t="n">
-        <v>277</v>
+        <v>297</v>
       </c>
       <c r="AJ25" t="n">
         <v>308</v>
@@ -3893,25 +3881,25 @@
         <v>398.84</v>
       </c>
       <c r="L26" t="n">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="M26" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="N26" t="n">
+        <v>18</v>
+      </c>
+      <c r="O26" t="n">
+        <v>20</v>
+      </c>
+      <c r="P26" t="n">
         <v>7</v>
       </c>
-      <c r="O26" t="n">
-        <v>19</v>
-      </c>
-      <c r="P26" t="n">
-        <v>11</v>
-      </c>
       <c r="Q26" t="n">
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -3926,28 +3914,28 @@
         <v>472</v>
       </c>
       <c r="W26" t="n">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="X26" t="n">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="Y26" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Z26" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB26" t="n">
         <v>7</v>
       </c>
-      <c r="AA26" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>11</v>
-      </c>
       <c r="AC26" t="n">
         <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -3962,7 +3950,7 @@
         <v>472</v>
       </c>
       <c r="AI26" t="n">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="AJ26" t="n">
         <v>419</v>
@@ -4027,13 +4015,13 @@
         <v>206.88</v>
       </c>
       <c r="L27" t="n">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="M27" t="n">
-        <v>217</v>
+        <v>242</v>
       </c>
       <c r="N27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4057,19 +4045,19 @@
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="W27" t="n">
-        <v>270</v>
+        <v>293</v>
       </c>
       <c r="X27" t="n">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="Y27" t="n">
-        <v>217</v>
+        <v>242</v>
       </c>
       <c r="Z27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -4093,10 +4081,10 @@
         <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="AI27" t="n">
-        <v>270</v>
+        <v>293</v>
       </c>
       <c r="AJ27" t="n">
         <v>342</v>
@@ -4161,19 +4149,19 @@
         <v>266.86</v>
       </c>
       <c r="L28" t="n">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="M28" t="n">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="N28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O28" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4185,31 +4173,31 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="W28" t="n">
-        <v>237</v>
+        <v>263</v>
       </c>
       <c r="X28" t="n">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="Y28" t="n">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="Z28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AA28" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4221,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AI28" t="n">
-        <v>237</v>
+        <v>263</v>
       </c>
       <c r="AJ28" t="n">
         <v>384</v>
@@ -4295,13 +4283,13 @@
         <v>341.76</v>
       </c>
       <c r="L29" t="n">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="M29" t="n">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="N29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4319,25 +4307,25 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="W29" t="n">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="X29" t="n">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="Y29" t="n">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="Z29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4355,16 +4343,16 @@
         <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="AI29" t="n">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="AJ29" t="n">
         <v>357</v>
@@ -4429,22 +4417,22 @@
         <v>166.76</v>
       </c>
       <c r="L30" t="n">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="M30" t="n">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="N30" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -4453,34 +4441,34 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>516</v>
+        <v>526</v>
       </c>
       <c r="W30" t="n">
-        <v>332</v>
+        <v>356</v>
       </c>
       <c r="X30" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="Y30" t="n">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
@@ -4495,10 +4483,10 @@
         <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="AI30" t="n">
-        <v>339</v>
+        <v>356</v>
       </c>
       <c r="AJ30" t="n">
         <v>457</v>
@@ -4566,13 +4554,13 @@
         <v>8</v>
       </c>
       <c r="M31" t="n">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="N31" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="O31" t="n">
-        <v>203</v>
+        <v>178</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
@@ -4596,19 +4584,19 @@
         <v>332</v>
       </c>
       <c r="W31" t="n">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="X31" t="n">
         <v>8</v>
       </c>
       <c r="Y31" t="n">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="Z31" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AA31" t="n">
-        <v>203</v>
+        <v>178</v>
       </c>
       <c r="AB31" t="n">
         <v>0</v>
@@ -4632,7 +4620,7 @@
         <v>332</v>
       </c>
       <c r="AI31" t="n">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="AJ31" t="n">
         <v>315</v>
@@ -4697,19 +4685,19 @@
         <v>345.92</v>
       </c>
       <c r="L32" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="M32" t="n">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="N32" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -4721,31 +4709,31 @@
         <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="U32" t="n">
         <v>3</v>
       </c>
       <c r="V32" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="W32" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="X32" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Y32" t="n">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="Z32" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4757,16 +4745,16 @@
         <v>1</v>
       </c>
       <c r="AF32" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="AG32" t="n">
         <v>3</v>
       </c>
       <c r="AH32" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AI32" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AJ32" t="n">
         <v>308</v>
@@ -4831,19 +4819,19 @@
         <v>340</v>
       </c>
       <c r="L33" t="n">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="M33" t="n">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="N33" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O33" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="P33" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -4855,31 +4843,31 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="W33" t="n">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="X33" t="n">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="Y33" t="n">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="Z33" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AA33" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB33" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4891,16 +4879,16 @@
         <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AI33" t="n">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="AJ33" t="n">
         <v>365</v>
@@ -4965,16 +4953,16 @@
         <v>263.95</v>
       </c>
       <c r="L34" t="n">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="M34" t="n">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
@@ -4989,28 +4977,28 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="W34" t="n">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="X34" t="n">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="Y34" t="n">
-        <v>298</v>
+        <v>316</v>
       </c>
       <c r="Z34" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>
@@ -5025,16 +5013,16 @@
         <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="AI34" t="n">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="AJ34" t="n">
         <v>410</v>
@@ -5099,13 +5087,13 @@
         <v>217.06</v>
       </c>
       <c r="L35" t="n">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="M35" t="n">
         <v>182</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5129,19 +5117,19 @@
         <v>1</v>
       </c>
       <c r="V35" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="W35" t="n">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="X35" t="n">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="Y35" t="n">
         <v>182</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5165,10 +5153,10 @@
         <v>1</v>
       </c>
       <c r="AH35" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AI35" t="n">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="AJ35" t="n">
         <v>303</v>
@@ -5233,13 +5221,13 @@
         <v>129.36</v>
       </c>
       <c r="L36" t="n">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="M36" t="n">
-        <v>217</v>
+        <v>246</v>
       </c>
       <c r="N36" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5263,19 +5251,19 @@
         <v>7</v>
       </c>
       <c r="V36" t="n">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="W36" t="n">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="X36" t="n">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="Y36" t="n">
-        <v>217</v>
+        <v>246</v>
       </c>
       <c r="Z36" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5299,10 +5287,10 @@
         <v>7</v>
       </c>
       <c r="AH36" t="n">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="AI36" t="n">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="AJ36" t="n">
         <v>412</v>
@@ -5367,16 +5355,16 @@
         <v>205.17</v>
       </c>
       <c r="L37" t="n">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="M37" t="n">
-        <v>276</v>
+        <v>318</v>
       </c>
       <c r="N37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
@@ -5391,28 +5379,28 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="W37" t="n">
-        <v>352</v>
+        <v>392</v>
       </c>
       <c r="X37" t="n">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="Y37" t="n">
-        <v>276</v>
+        <v>318</v>
       </c>
       <c r="Z37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
         <v>0</v>
@@ -5427,16 +5415,16 @@
         <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="AI37" t="n">
-        <v>352</v>
+        <v>392</v>
       </c>
       <c r="AJ37" t="n">
         <v>371</v>
@@ -5501,19 +5489,19 @@
         <v>328.87</v>
       </c>
       <c r="L38" t="n">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="M38" t="n">
-        <v>194</v>
+        <v>228</v>
       </c>
       <c r="N38" t="n">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="O38" t="n">
         <v>2</v>
       </c>
       <c r="P38" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -5531,25 +5519,25 @@
         <v>4</v>
       </c>
       <c r="V38" t="n">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="W38" t="n">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="X38" t="n">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="Y38" t="n">
-        <v>194</v>
+        <v>225</v>
       </c>
       <c r="Z38" t="n">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="AA38" t="n">
         <v>2</v>
       </c>
       <c r="AB38" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5567,10 +5555,10 @@
         <v>4</v>
       </c>
       <c r="AH38" t="n">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="AI38" t="n">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="AJ38" t="n">
         <v>453</v>
@@ -5635,22 +5623,22 @@
         <v>276.26</v>
       </c>
       <c r="L39" t="n">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="M39" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="N39" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="O39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P39" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="Q39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>1</v>
@@ -5668,25 +5656,25 @@
         <v>474</v>
       </c>
       <c r="W39" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="X39" t="n">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="Y39" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="Z39" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="AA39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB39" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="AC39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
         <v>1</v>
@@ -5704,7 +5692,7 @@
         <v>474</v>
       </c>
       <c r="AI39" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="AJ39" t="n">
         <v>445</v>
@@ -5769,19 +5757,19 @@
         <v>167.42</v>
       </c>
       <c r="L40" t="n">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="M40" t="n">
-        <v>251</v>
+        <v>273</v>
       </c>
       <c r="N40" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -5799,25 +5787,25 @@
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="W40" t="n">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="X40" t="n">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="Y40" t="n">
-        <v>251</v>
+        <v>273</v>
       </c>
       <c r="Z40" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5835,10 +5823,10 @@
         <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AI40" t="n">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="AJ40" t="n">
         <v>379</v>
@@ -5903,13 +5891,13 @@
         <v>340.01</v>
       </c>
       <c r="L41" t="n">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="M41" t="n">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="N41" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5933,19 +5921,19 @@
         <v>1</v>
       </c>
       <c r="V41" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="W41" t="n">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="X41" t="n">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="Y41" t="n">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="Z41" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5969,10 +5957,10 @@
         <v>1</v>
       </c>
       <c r="AH41" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AI41" t="n">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="AJ41" t="n">
         <v>335</v>
@@ -6037,16 +6025,16 @@
         <v>113.26</v>
       </c>
       <c r="L42" t="n">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="M42" t="n">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="N42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="P42" t="n">
         <v>0</v>
@@ -6061,28 +6049,28 @@
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V42" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="W42" t="n">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="X42" t="n">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="Y42" t="n">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="Z42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AB42" t="n">
         <v>0</v>
@@ -6097,16 +6085,16 @@
         <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH42" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AI42" t="n">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="AJ42" t="n">
         <v>371</v>
@@ -6171,19 +6159,19 @@
         <v>354.19</v>
       </c>
       <c r="L43" t="n">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="M43" t="n">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="N43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -6201,25 +6189,25 @@
         <v>1</v>
       </c>
       <c r="V43" t="n">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="W43" t="n">
-        <v>286</v>
+        <v>301</v>
       </c>
       <c r="X43" t="n">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="Y43" t="n">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="Z43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -6237,10 +6225,10 @@
         <v>1</v>
       </c>
       <c r="AH43" t="n">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="AI43" t="n">
-        <v>286</v>
+        <v>301</v>
       </c>
       <c r="AJ43" t="n">
         <v>331</v>
@@ -6305,19 +6293,19 @@
         <v>335.27</v>
       </c>
       <c r="L44" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="M44" t="n">
-        <v>231</v>
+        <v>259</v>
       </c>
       <c r="N44" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -6335,25 +6323,25 @@
         <v>3</v>
       </c>
       <c r="V44" t="n">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="W44" t="n">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="X44" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="Y44" t="n">
-        <v>231</v>
+        <v>259</v>
       </c>
       <c r="Z44" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -6371,10 +6359,10 @@
         <v>3</v>
       </c>
       <c r="AH44" t="n">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI44" t="n">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="AJ44" t="n">
         <v>301</v>
@@ -6439,16 +6427,16 @@
         <v>198.34</v>
       </c>
       <c r="L45" t="n">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="M45" t="n">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="N45" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="O45" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="P45" t="n">
         <v>87</v>
@@ -6469,22 +6457,22 @@
         <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="W45" t="n">
-        <v>289</v>
+        <v>312</v>
       </c>
       <c r="X45" t="n">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="Y45" t="n">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="Z45" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AA45" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AB45" t="n">
         <v>0</v>
@@ -6505,10 +6493,10 @@
         <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="AI45" t="n">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="AJ45" t="n">
         <v>355</v>
@@ -6573,13 +6561,13 @@
         <v>324.84</v>
       </c>
       <c r="L46" t="n">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="M46" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N46" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="O46" t="n">
         <v>2</v>
@@ -6597,25 +6585,25 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="U46" t="n">
         <v>6</v>
       </c>
       <c r="V46" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="W46" t="n">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="X46" t="n">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="Y46" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Z46" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="AA46" t="n">
         <v>2</v>
@@ -6633,16 +6621,16 @@
         <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AG46" t="n">
         <v>6</v>
       </c>
       <c r="AH46" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AI46" t="n">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="AJ46" t="n">
         <v>434</v>
@@ -6710,13 +6698,13 @@
         <v>170</v>
       </c>
       <c r="M47" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P47" t="n">
         <v>0</v>
@@ -6731,28 +6719,28 @@
         <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="W47" t="n">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="X47" t="n">
         <v>170</v>
       </c>
       <c r="Y47" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="Z47" t="n">
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AB47" t="n">
         <v>0</v>
@@ -6767,16 +6755,16 @@
         <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="AI47" t="n">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="AJ47" t="n">
         <v>375</v>
@@ -6841,19 +6829,19 @@
         <v>245.52</v>
       </c>
       <c r="L48" t="n">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="M48" t="n">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="N48" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="O48" t="n">
         <v>1</v>
       </c>
       <c r="P48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -6865,31 +6853,31 @@
         <v>0</v>
       </c>
       <c r="T48" t="n">
+        <v>41</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>414</v>
+      </c>
+      <c r="W48" t="n">
+        <v>200</v>
+      </c>
+      <c r="X48" t="n">
+        <v>213</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>134</v>
+      </c>
+      <c r="Z48" t="n">
         <v>24</v>
       </c>
-      <c r="U48" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" t="n">
-        <v>413</v>
-      </c>
-      <c r="W48" t="n">
-        <v>192</v>
-      </c>
-      <c r="X48" t="n">
-        <v>220</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>145</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>22</v>
-      </c>
       <c r="AA48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6901,16 +6889,16 @@
         <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI48" t="n">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="AJ48" t="n">
         <v>363</v>
@@ -6978,7 +6966,7 @@
         <v>211</v>
       </c>
       <c r="M49" t="n">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
@@ -6987,7 +6975,7 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -6999,7 +6987,7 @@
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="U49" t="n">
         <v>0</v>
@@ -7014,10 +7002,10 @@
         <v>211</v>
       </c>
       <c r="Y49" t="n">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="Z49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -7035,7 +7023,7 @@
         <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -7109,19 +7097,19 @@
         <v>240.68</v>
       </c>
       <c r="L50" t="n">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="M50" t="n">
         <v>192</v>
       </c>
       <c r="N50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -7133,7 +7121,7 @@
         <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="U50" t="n">
         <v>2</v>
@@ -7142,22 +7130,22 @@
         <v>450</v>
       </c>
       <c r="W50" t="n">
+        <v>226</v>
+      </c>
+      <c r="X50" t="n">
         <v>224</v>
-      </c>
-      <c r="X50" t="n">
-        <v>226</v>
       </c>
       <c r="Y50" t="n">
         <v>192</v>
       </c>
       <c r="Z50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -7169,7 +7157,7 @@
         <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AG50" t="n">
         <v>2</v>
@@ -7178,7 +7166,7 @@
         <v>450</v>
       </c>
       <c r="AI50" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AJ50" t="n">
         <v>372</v>
@@ -7243,19 +7231,19 @@
         <v>224.16</v>
       </c>
       <c r="L51" t="n">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="M51" t="n">
-        <v>368</v>
+        <v>346</v>
       </c>
       <c r="N51" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="O51" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -7267,31 +7255,31 @@
         <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="U51" t="n">
         <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="W51" t="n">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="X51" t="n">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="Y51" t="n">
-        <v>368</v>
+        <v>346</v>
       </c>
       <c r="Z51" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="AA51" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -7303,16 +7291,16 @@
         <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
       </c>
       <c r="AH51" t="n">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="AI51" t="n">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="AJ51" t="n">
         <v>395</v>
@@ -7377,13 +7365,13 @@
         <v>237.21</v>
       </c>
       <c r="L52" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="M52" t="n">
-        <v>214</v>
+        <v>247</v>
       </c>
       <c r="N52" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7401,25 +7389,25 @@
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="U52" t="n">
         <v>1</v>
       </c>
       <c r="V52" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="W52" t="n">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="X52" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="Y52" t="n">
-        <v>214</v>
+        <v>247</v>
       </c>
       <c r="Z52" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7437,16 +7425,16 @@
         <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AG52" t="n">
         <v>1</v>
       </c>
       <c r="AH52" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="AI52" t="n">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="AJ52" t="n">
         <v>378</v>
@@ -7511,16 +7499,16 @@
         <v>285.04</v>
       </c>
       <c r="L53" t="n">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="M53" t="n">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="N53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P53" t="n">
         <v>0</v>
@@ -7541,19 +7529,19 @@
         <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="W53" t="n">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="X53" t="n">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="Y53" t="n">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="Z53" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AA53" t="n">
         <v>5</v>
@@ -7577,10 +7565,10 @@
         <v>0</v>
       </c>
       <c r="AH53" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AI53" t="n">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="AJ53" t="n">
         <v>429</v>
@@ -7645,16 +7633,16 @@
         <v>370.43</v>
       </c>
       <c r="L54" t="n">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="M54" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="N54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O54" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P54" t="n">
         <v>22</v>
@@ -7678,19 +7666,19 @@
         <v>424</v>
       </c>
       <c r="W54" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="X54" t="n">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="Y54" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="Z54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA54" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AB54" t="n">
         <v>22</v>
@@ -7714,7 +7702,7 @@
         <v>424</v>
       </c>
       <c r="AI54" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="AJ54" t="n">
         <v>396</v>
@@ -7779,25 +7767,25 @@
         <v>417.22</v>
       </c>
       <c r="L55" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M55" t="n">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="N55" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>1</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -7812,28 +7800,28 @@
         <v>374</v>
       </c>
       <c r="W55" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="X55" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Y55" t="n">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="Z55" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
         <v>1</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE55" t="n">
         <v>0</v>
@@ -7848,7 +7836,7 @@
         <v>374</v>
       </c>
       <c r="AI55" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AJ55" t="n">
         <v>279</v>
@@ -7913,19 +7901,19 @@
         <v>176.57</v>
       </c>
       <c r="L56" t="n">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="M56" t="n">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="N56" t="n">
         <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="P56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -7937,31 +7925,31 @@
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="U56" t="n">
         <v>1</v>
       </c>
       <c r="V56" t="n">
-        <v>527</v>
+        <v>544</v>
       </c>
       <c r="W56" t="n">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="X56" t="n">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="Y56" t="n">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="Z56" t="n">
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AB56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7973,16 +7961,16 @@
         <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="AG56" t="n">
         <v>1</v>
       </c>
       <c r="AH56" t="n">
-        <v>527</v>
+        <v>544</v>
       </c>
       <c r="AI56" t="n">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="AJ56" t="n">
         <v>420</v>
@@ -8047,16 +8035,16 @@
         <v>284.32</v>
       </c>
       <c r="L57" t="n">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="M57" t="n">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="N57" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O57" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P57" t="n">
         <v>1</v>
@@ -8071,28 +8059,28 @@
         <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="U57" t="n">
         <v>0</v>
       </c>
       <c r="V57" t="n">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="W57" t="n">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="X57" t="n">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="Y57" t="n">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="Z57" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AA57" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AB57" t="n">
         <v>1</v>
@@ -8107,16 +8095,16 @@
         <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
       </c>
       <c r="AH57" t="n">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="AI57" t="n">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="AJ57" t="n">
         <v>336</v>
@@ -8181,22 +8169,22 @@
         <v>130.92</v>
       </c>
       <c r="L58" t="n">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="M58" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="N58" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
@@ -8205,34 +8193,34 @@
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="U58" t="n">
         <v>2</v>
       </c>
       <c r="V58" t="n">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="W58" t="n">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="X58" t="n">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="Y58" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="Z58" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD58" t="n">
         <v>0</v>
@@ -8241,16 +8229,16 @@
         <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AG58" t="n">
         <v>2</v>
       </c>
       <c r="AH58" t="n">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="AI58" t="n">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="AJ58" t="n">
         <v>363</v>
@@ -8315,16 +8303,16 @@
         <v>149.53</v>
       </c>
       <c r="L59" t="n">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="M59" t="n">
         <v>153</v>
       </c>
       <c r="N59" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="O59" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="P59" t="n">
         <v>0</v>
@@ -8345,22 +8333,22 @@
         <v>4</v>
       </c>
       <c r="V59" t="n">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="W59" t="n">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="X59" t="n">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="Y59" t="n">
         <v>153</v>
       </c>
       <c r="Z59" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="AA59" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AB59" t="n">
         <v>0</v>
@@ -8381,10 +8369,10 @@
         <v>4</v>
       </c>
       <c r="AH59" t="n">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AI59" t="n">
-        <v>251</v>
+        <v>269</v>
       </c>
       <c r="AJ59" t="n">
         <v>383</v>
@@ -8449,76 +8437,76 @@
         <v>116.67</v>
       </c>
       <c r="L60" t="n">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="M60" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="N60" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="O60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P60" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="Q60" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="U60" t="n">
         <v>0</v>
       </c>
       <c r="V60" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="W60" t="n">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="X60" t="n">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="Y60" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="Z60" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AA60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB60" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AC60" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE60" t="n">
         <v>0</v>
       </c>
       <c r="AF60" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
       </c>
       <c r="AH60" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AI60" t="n">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="AJ60" t="n">
         <v>377</v>
@@ -8717,22 +8705,22 @@
         <v>253.72</v>
       </c>
       <c r="L62" t="n">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="M62" t="n">
-        <v>247</v>
+        <v>296</v>
       </c>
       <c r="N62" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>1</v>
       </c>
       <c r="P62" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
@@ -8747,28 +8735,28 @@
         <v>0</v>
       </c>
       <c r="V62" t="n">
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="W62" t="n">
-        <v>334</v>
+        <v>354</v>
       </c>
       <c r="X62" t="n">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="Y62" t="n">
-        <v>247</v>
+        <v>296</v>
       </c>
       <c r="Z62" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AA62" t="n">
         <v>1</v>
       </c>
       <c r="AB62" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AC62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD62" t="n">
         <v>0</v>
@@ -8783,10 +8771,10 @@
         <v>0</v>
       </c>
       <c r="AH62" t="n">
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="AI62" t="n">
-        <v>334</v>
+        <v>354</v>
       </c>
       <c r="AJ62" t="n">
         <v>365</v>
@@ -8851,13 +8839,13 @@
         <v>125.98</v>
       </c>
       <c r="L63" t="n">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="M63" t="n">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="N63" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8881,19 +8869,19 @@
         <v>0</v>
       </c>
       <c r="V63" t="n">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="W63" t="n">
-        <v>285</v>
+        <v>303</v>
       </c>
       <c r="X63" t="n">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="Y63" t="n">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="Z63" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8917,10 +8905,10 @@
         <v>0</v>
       </c>
       <c r="AH63" t="n">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="AI63" t="n">
-        <v>284</v>
+        <v>303</v>
       </c>
       <c r="AJ63" t="n">
         <v>324</v>
@@ -8985,19 +8973,19 @@
         <v>167.78</v>
       </c>
       <c r="L64" t="n">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="M64" t="n">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -9015,16 +9003,16 @@
         <v>2</v>
       </c>
       <c r="V64" t="n">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="W64" t="n">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="X64" t="n">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="Y64" t="n">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="Z64" t="n">
         <v>0</v>
@@ -9033,7 +9021,7 @@
         <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -9051,10 +9039,10 @@
         <v>2</v>
       </c>
       <c r="AH64" t="n">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="AI64" t="n">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="AJ64" t="n">
         <v>440</v>
@@ -9119,19 +9107,19 @@
         <v>225.78</v>
       </c>
       <c r="L65" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M65" t="n">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="N65" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -9149,25 +9137,25 @@
         <v>0</v>
       </c>
       <c r="V65" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="W65" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="X65" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Y65" t="n">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="Z65" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -9185,10 +9173,10 @@
         <v>0</v>
       </c>
       <c r="AH65" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AI65" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AJ65" t="n">
         <v>417</v>
@@ -9253,19 +9241,19 @@
         <v>191.03</v>
       </c>
       <c r="L66" t="n">
-        <v>209</v>
+        <v>170</v>
       </c>
       <c r="M66" t="n">
-        <v>213</v>
+        <v>253</v>
       </c>
       <c r="N66" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -9280,28 +9268,28 @@
         <v>21</v>
       </c>
       <c r="U66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V66" t="n">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="W66" t="n">
-        <v>240</v>
+        <v>282</v>
       </c>
       <c r="X66" t="n">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="Y66" t="n">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="Z66" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -9319,10 +9307,10 @@
         <v>1</v>
       </c>
       <c r="AH66" t="n">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AI66" t="n">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="AJ66" t="n">
         <v>384</v>
@@ -9387,19 +9375,19 @@
         <v>282.09</v>
       </c>
       <c r="L67" t="n">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="M67" t="n">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="N67" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -9417,25 +9405,25 @@
         <v>5</v>
       </c>
       <c r="V67" t="n">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="W67" t="n">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="X67" t="n">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="Y67" t="n">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="Z67" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -9453,10 +9441,10 @@
         <v>5</v>
       </c>
       <c r="AH67" t="n">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="AI67" t="n">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="AJ67" t="n">
         <v>297</v>
@@ -9521,19 +9509,19 @@
         <v>104.5</v>
       </c>
       <c r="L68" t="n">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="M68" t="n">
-        <v>363</v>
+        <v>414</v>
       </c>
       <c r="N68" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="O68" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -9545,31 +9533,31 @@
         <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="U68" t="n">
         <v>0</v>
       </c>
       <c r="V68" t="n">
-        <v>506</v>
+        <v>516</v>
       </c>
       <c r="W68" t="n">
-        <v>417</v>
+        <v>458</v>
       </c>
       <c r="X68" t="n">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="Y68" t="n">
-        <v>363</v>
+        <v>414</v>
       </c>
       <c r="Z68" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="AA68" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -9581,16 +9569,16 @@
         <v>0</v>
       </c>
       <c r="AF68" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
       </c>
       <c r="AH68" t="n">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="AI68" t="n">
-        <v>417</v>
+        <v>458</v>
       </c>
       <c r="AJ68" t="n">
         <v>395</v>
@@ -9655,19 +9643,19 @@
         <v>107.39</v>
       </c>
       <c r="L69" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M69" t="n">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="N69" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="O69" t="n">
         <v>1</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -9679,31 +9667,31 @@
         <v>0</v>
       </c>
       <c r="T69" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U69" t="n">
         <v>0</v>
       </c>
       <c r="V69" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="W69" t="n">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="X69" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="Y69" t="n">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="Z69" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="AA69" t="n">
         <v>1</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -9715,16 +9703,16 @@
         <v>0</v>
       </c>
       <c r="AF69" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
       </c>
       <c r="AH69" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AI69" t="n">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="AJ69" t="n">
         <v>317</v>
@@ -9789,19 +9777,19 @@
         <v>98.48999999999999</v>
       </c>
       <c r="L70" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="M70" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -9822,22 +9810,22 @@
         <v>346</v>
       </c>
       <c r="W70" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="X70" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="Y70" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="Z70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -9858,7 +9846,7 @@
         <v>346</v>
       </c>
       <c r="AI70" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AJ70" t="n">
         <v>306</v>
@@ -9923,16 +9911,16 @@
         <v>240.64</v>
       </c>
       <c r="L71" t="n">
-        <v>171</v>
+        <v>150</v>
       </c>
       <c r="M71" t="n">
-        <v>276</v>
+        <v>295</v>
       </c>
       <c r="N71" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O71" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="P71" t="n">
         <v>0</v>
@@ -9953,22 +9941,22 @@
         <v>1</v>
       </c>
       <c r="V71" t="n">
-        <v>500</v>
+        <v>514</v>
       </c>
       <c r="W71" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="X71" t="n">
-        <v>171</v>
+        <v>150</v>
       </c>
       <c r="Y71" t="n">
-        <v>276</v>
+        <v>295</v>
       </c>
       <c r="Z71" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AA71" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="AB71" t="n">
         <v>0</v>
@@ -9989,10 +9977,10 @@
         <v>1</v>
       </c>
       <c r="AH71" t="n">
-        <v>500</v>
+        <v>514</v>
       </c>
       <c r="AI71" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="AJ71" t="n">
         <v>366</v>
@@ -10057,16 +10045,16 @@
         <v>264.67</v>
       </c>
       <c r="L72" t="n">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="M72" t="n">
-        <v>411</v>
+        <v>451</v>
       </c>
       <c r="N72" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P72" t="n">
         <v>0</v>
@@ -10087,22 +10075,22 @@
         <v>0</v>
       </c>
       <c r="V72" t="n">
-        <v>542</v>
+        <v>551</v>
       </c>
       <c r="W72" t="n">
-        <v>465</v>
+        <v>502</v>
       </c>
       <c r="X72" t="n">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="Y72" t="n">
-        <v>411</v>
+        <v>451</v>
       </c>
       <c r="Z72" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB72" t="n">
         <v>0</v>
@@ -10123,10 +10111,10 @@
         <v>0</v>
       </c>
       <c r="AH72" t="n">
-        <v>542</v>
+        <v>551</v>
       </c>
       <c r="AI72" t="n">
-        <v>465</v>
+        <v>502</v>
       </c>
       <c r="AJ72" t="n">
         <v>353</v>
@@ -10191,10 +10179,10 @@
         <v>193.05</v>
       </c>
       <c r="L73" t="n">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="M73" t="n">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="N73" t="n">
         <v>0</v>
@@ -10215,22 +10203,22 @@
         <v>0</v>
       </c>
       <c r="T73" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="U73" t="n">
         <v>1</v>
       </c>
       <c r="V73" t="n">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="W73" t="n">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="X73" t="n">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="Y73" t="n">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="Z73" t="n">
         <v>0</v>
@@ -10251,16 +10239,16 @@
         <v>0</v>
       </c>
       <c r="AF73" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="AG73" t="n">
         <v>1</v>
       </c>
       <c r="AH73" t="n">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AI73" t="n">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="AJ73" t="n">
         <v>362</v>
@@ -10325,16 +10313,16 @@
         <v>218.56</v>
       </c>
       <c r="L74" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="M74" t="n">
-        <v>286</v>
+        <v>312</v>
       </c>
       <c r="N74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="P74" t="n">
         <v>0</v>
@@ -10349,28 +10337,28 @@
         <v>0</v>
       </c>
       <c r="T74" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="U74" t="n">
         <v>1</v>
       </c>
       <c r="V74" t="n">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="W74" t="n">
-        <v>351</v>
+        <v>377</v>
       </c>
       <c r="X74" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y74" t="n">
-        <v>286</v>
+        <v>312</v>
       </c>
       <c r="Z74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="AB74" t="n">
         <v>0</v>
@@ -10385,16 +10373,16 @@
         <v>0</v>
       </c>
       <c r="AF74" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AG74" t="n">
         <v>1</v>
       </c>
       <c r="AH74" t="n">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AI74" t="n">
-        <v>351</v>
+        <v>377</v>
       </c>
       <c r="AJ74" t="n">
         <v>398</v>
@@ -10459,55 +10447,55 @@
         <v>132.3</v>
       </c>
       <c r="L75" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="M75" t="n">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="N75" t="n">
+        <v>5</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>31</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>413</v>
+      </c>
+      <c r="W75" t="n">
+        <v>251</v>
+      </c>
+      <c r="X75" t="n">
+        <v>161</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>214</v>
+      </c>
+      <c r="Z75" t="n">
         <v>4</v>
       </c>
-      <c r="O75" t="n">
-        <v>3</v>
-      </c>
-      <c r="P75" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
-      <c r="R75" t="n">
-        <v>0</v>
-      </c>
-      <c r="S75" t="n">
-        <v>0</v>
-      </c>
-      <c r="T75" t="n">
-        <v>30</v>
-      </c>
-      <c r="U75" t="n">
-        <v>0</v>
-      </c>
-      <c r="V75" t="n">
-        <v>411</v>
-      </c>
-      <c r="W75" t="n">
-        <v>245</v>
-      </c>
-      <c r="X75" t="n">
-        <v>164</v>
-      </c>
-      <c r="Y75" t="n">
-        <v>202</v>
-      </c>
-      <c r="Z75" t="n">
-        <v>3</v>
-      </c>
       <c r="AA75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB75" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -10519,16 +10507,16 @@
         <v>0</v>
       </c>
       <c r="AF75" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
       </c>
       <c r="AH75" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AI75" t="n">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="AJ75" t="n">
         <v>359</v>
@@ -10593,13 +10581,13 @@
         <v>93.08</v>
       </c>
       <c r="L76" t="n">
-        <v>240</v>
+        <v>217</v>
       </c>
       <c r="M76" t="n">
         <v>133</v>
       </c>
       <c r="N76" t="n">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10623,19 +10611,19 @@
         <v>0</v>
       </c>
       <c r="V76" t="n">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="W76" t="n">
-        <v>168</v>
+        <v>197</v>
       </c>
       <c r="X76" t="n">
-        <v>240</v>
+        <v>217</v>
       </c>
       <c r="Y76" t="n">
         <v>133</v>
       </c>
       <c r="Z76" t="n">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>
@@ -10659,10 +10647,10 @@
         <v>0</v>
       </c>
       <c r="AH76" t="n">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="AI76" t="n">
-        <v>168</v>
+        <v>197</v>
       </c>
       <c r="AJ76" t="n">
         <v>357</v>
@@ -10727,19 +10715,19 @@
         <v>177.39</v>
       </c>
       <c r="L77" t="n">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="M77" t="n">
-        <v>240</v>
+        <v>296</v>
       </c>
       <c r="N77" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
@@ -10751,31 +10739,31 @@
         <v>0</v>
       </c>
       <c r="T77" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="U77" t="n">
         <v>0</v>
       </c>
       <c r="V77" t="n">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="W77" t="n">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="X77" t="n">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="Y77" t="n">
-        <v>240</v>
+        <v>296</v>
       </c>
       <c r="Z77" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AA77" t="n">
         <v>9</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -10787,16 +10775,16 @@
         <v>0</v>
       </c>
       <c r="AF77" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
       </c>
       <c r="AH77" t="n">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AI77" t="n">
-        <v>347</v>
+        <v>362</v>
       </c>
       <c r="AJ77" t="n">
         <v>386</v>
@@ -10861,19 +10849,19 @@
         <v>132.61</v>
       </c>
       <c r="L78" t="n">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="M78" t="n">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="N78" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
@@ -10885,31 +10873,31 @@
         <v>0</v>
       </c>
       <c r="T78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U78" t="n">
         <v>1</v>
       </c>
       <c r="V78" t="n">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="W78" t="n">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="X78" t="n">
         <v>150</v>
       </c>
       <c r="Y78" t="n">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Z78" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -10921,16 +10909,16 @@
         <v>0</v>
       </c>
       <c r="AF78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG78" t="n">
         <v>1</v>
       </c>
       <c r="AH78" t="n">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="AI78" t="n">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="AJ78" t="n">
         <v>350</v>
@@ -10995,13 +10983,13 @@
         <v>422.38</v>
       </c>
       <c r="L79" t="n">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="M79" t="n">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="N79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -11025,19 +11013,19 @@
         <v>0</v>
       </c>
       <c r="V79" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="W79" t="n">
-        <v>299</v>
+        <v>315</v>
       </c>
       <c r="X79" t="n">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="Y79" t="n">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="Z79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -11061,10 +11049,10 @@
         <v>0</v>
       </c>
       <c r="AH79" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="AI79" t="n">
-        <v>299</v>
+        <v>315</v>
       </c>
       <c r="AJ79" t="n">
         <v>319</v>
@@ -11132,7 +11120,7 @@
         <v>96</v>
       </c>
       <c r="M80" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="N80" t="n">
         <v>0</v>
@@ -11141,7 +11129,7 @@
         <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
@@ -11168,7 +11156,7 @@
         <v>96</v>
       </c>
       <c r="Y80" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="Z80" t="n">
         <v>0</v>
@@ -11177,7 +11165,7 @@
         <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -11397,19 +11385,19 @@
         <v>414.19</v>
       </c>
       <c r="L82" t="n">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="M82" t="n">
         <v>218</v>
       </c>
       <c r="N82" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q82" t="n">
         <v>0</v>
@@ -11427,25 +11415,25 @@
         <v>0</v>
       </c>
       <c r="V82" t="n">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="W82" t="n">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="X82" t="n">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="Y82" t="n">
         <v>218</v>
       </c>
       <c r="Z82" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -11463,10 +11451,10 @@
         <v>0</v>
       </c>
       <c r="AH82" t="n">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="AI82" t="n">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="AJ82" t="n">
         <v>385</v>
@@ -11531,19 +11519,19 @@
         <v>240.59</v>
       </c>
       <c r="L83" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="M83" t="n">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="N83" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
@@ -11561,25 +11549,25 @@
         <v>0</v>
       </c>
       <c r="V83" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="W83" t="n">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="X83" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="Y83" t="n">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="Z83" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="AA83" t="n">
         <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -11597,10 +11585,10 @@
         <v>0</v>
       </c>
       <c r="AH83" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AI83" t="n">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="AJ83" t="n">
         <v>340</v>
@@ -11665,16 +11653,16 @@
         <v>153.17</v>
       </c>
       <c r="L84" t="n">
-        <v>196</v>
+        <v>177</v>
       </c>
       <c r="M84" t="n">
-        <v>218</v>
+        <v>242</v>
       </c>
       <c r="N84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="P84" t="n">
         <v>0</v>
@@ -11689,28 +11677,28 @@
         <v>0</v>
       </c>
       <c r="T84" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U84" t="n">
         <v>0</v>
       </c>
       <c r="V84" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="W84" t="n">
-        <v>226</v>
+        <v>253</v>
       </c>
       <c r="X84" t="n">
-        <v>196</v>
+        <v>177</v>
       </c>
       <c r="Y84" t="n">
-        <v>218</v>
+        <v>242</v>
       </c>
       <c r="Z84" t="n">
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="AB84" t="n">
         <v>0</v>
@@ -11725,16 +11713,16 @@
         <v>0</v>
       </c>
       <c r="AF84" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
       </c>
       <c r="AH84" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AI84" t="n">
-        <v>225</v>
+        <v>253</v>
       </c>
       <c r="AJ84" t="n">
         <v>378</v>
@@ -11799,13 +11787,13 @@
         <v>270.06</v>
       </c>
       <c r="L85" t="n">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="M85" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="N85" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11823,25 +11811,25 @@
         <v>0</v>
       </c>
       <c r="T85" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="U85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V85" t="n">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="W85" t="n">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="X85" t="n">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="Y85" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="Z85" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA85" t="n">
         <v>0</v>
@@ -11859,16 +11847,16 @@
         <v>0</v>
       </c>
       <c r="AF85" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="AG85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH85" t="n">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="AI85" t="n">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="AJ85" t="n">
         <v>367</v>
@@ -11933,22 +11921,22 @@
         <v>135</v>
       </c>
       <c r="L86" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="M86" t="n">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="N86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O86" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="P86" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="Q86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
         <v>0</v>
@@ -11957,7 +11945,7 @@
         <v>0</v>
       </c>
       <c r="T86" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="U86" t="n">
         <v>0</v>
@@ -11966,25 +11954,25 @@
         <v>447</v>
       </c>
       <c r="W86" t="n">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="X86" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="Y86" t="n">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="Z86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB86" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="AC86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD86" t="n">
         <v>0</v>
@@ -11993,7 +11981,7 @@
         <v>0</v>
       </c>
       <c r="AF86" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -12002,7 +11990,7 @@
         <v>447</v>
       </c>
       <c r="AI86" t="n">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="AJ86" t="n">
         <v>367</v>
@@ -12067,16 +12055,16 @@
         <v>174.07</v>
       </c>
       <c r="L87" t="n">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="M87" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N87" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O87" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="P87" t="n">
         <v>27</v>
@@ -12091,28 +12079,28 @@
         <v>0</v>
       </c>
       <c r="T87" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="U87" t="n">
         <v>0</v>
       </c>
       <c r="V87" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="W87" t="n">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="X87" t="n">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="Y87" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Z87" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AA87" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AB87" t="n">
         <v>27</v>
@@ -12127,16 +12115,16 @@
         <v>0</v>
       </c>
       <c r="AF87" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
       </c>
       <c r="AH87" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AI87" t="n">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="AJ87" t="n">
         <v>360</v>
@@ -12201,16 +12189,16 @@
         <v>162.12</v>
       </c>
       <c r="L88" t="n">
-        <v>144</v>
+        <v>113</v>
       </c>
       <c r="M88" t="n">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="N88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O88" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="P88" t="n">
         <v>1</v>
@@ -12225,28 +12213,28 @@
         <v>0</v>
       </c>
       <c r="T88" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="U88" t="n">
         <v>0</v>
       </c>
       <c r="V88" t="n">
-        <v>441</v>
+        <v>452</v>
       </c>
       <c r="W88" t="n">
-        <v>264</v>
+        <v>286</v>
       </c>
       <c r="X88" t="n">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="Y88" t="n">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="Z88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA88" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="AB88" t="n">
         <v>1</v>
@@ -12261,16 +12249,16 @@
         <v>0</v>
       </c>
       <c r="AF88" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
       </c>
       <c r="AH88" t="n">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="AI88" t="n">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="AJ88" t="n">
         <v>356</v>
@@ -12335,19 +12323,19 @@
         <v>218.33</v>
       </c>
       <c r="L89" t="n">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="M89" t="n">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="N89" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="O89" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
@@ -12359,7 +12347,7 @@
         <v>0</v>
       </c>
       <c r="T89" t="n">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="U89" t="n">
         <v>0</v>
@@ -12368,22 +12356,22 @@
         <v>492</v>
       </c>
       <c r="W89" t="n">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="X89" t="n">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="Y89" t="n">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Z89" t="n">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="AA89" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AB89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -12395,7 +12383,7 @@
         <v>0</v>
       </c>
       <c r="AF89" t="n">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -12404,7 +12392,7 @@
         <v>492</v>
       </c>
       <c r="AI89" t="n">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="AJ89" t="n">
         <v>405</v>
@@ -12469,16 +12457,16 @@
         <v>364.57</v>
       </c>
       <c r="L90" t="n">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="M90" t="n">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="N90" t="n">
         <v>0</v>
       </c>
       <c r="O90" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="P90" t="n">
         <v>0</v>
@@ -12493,28 +12481,28 @@
         <v>0</v>
       </c>
       <c r="T90" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V90" t="n">
         <v>323</v>
       </c>
       <c r="W90" t="n">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="X90" t="n">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="Y90" t="n">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="Z90" t="n">
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="AB90" t="n">
         <v>0</v>
@@ -12529,16 +12517,16 @@
         <v>0</v>
       </c>
       <c r="AF90" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH90" t="n">
         <v>323</v>
       </c>
       <c r="AI90" t="n">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="AJ90" t="n">
         <v>301</v>
@@ -12603,13 +12591,13 @@
         <v>216.08</v>
       </c>
       <c r="L91" t="n">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="M91" t="n">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="N91" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12633,19 +12621,19 @@
         <v>0</v>
       </c>
       <c r="V91" t="n">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="W91" t="n">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="X91" t="n">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="Y91" t="n">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="Z91" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12669,10 +12657,10 @@
         <v>0</v>
       </c>
       <c r="AH91" t="n">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="AI91" t="n">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="AJ91" t="n">
         <v>399</v>
@@ -12737,13 +12725,13 @@
         <v>199.37</v>
       </c>
       <c r="L92" t="n">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="M92" t="n">
-        <v>213</v>
+        <v>262</v>
       </c>
       <c r="N92" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>5</v>
@@ -12767,19 +12755,19 @@
         <v>0</v>
       </c>
       <c r="V92" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="W92" t="n">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="X92" t="n">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="Y92" t="n">
-        <v>213</v>
+        <v>262</v>
       </c>
       <c r="Z92" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="AA92" t="n">
         <v>5</v>
@@ -12803,10 +12791,10 @@
         <v>0</v>
       </c>
       <c r="AH92" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AI92" t="n">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="AJ92" t="n">
         <v>364</v>
@@ -12871,10 +12859,10 @@
         <v>339.58</v>
       </c>
       <c r="L93" t="n">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="M93" t="n">
-        <v>240</v>
+        <v>263</v>
       </c>
       <c r="N93" t="n">
         <v>0</v>
@@ -12883,7 +12871,7 @@
         <v>0</v>
       </c>
       <c r="P93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
@@ -12901,16 +12889,16 @@
         <v>0</v>
       </c>
       <c r="V93" t="n">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="W93" t="n">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="X93" t="n">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="Y93" t="n">
-        <v>240</v>
+        <v>263</v>
       </c>
       <c r="Z93" t="n">
         <v>0</v>
@@ -12919,7 +12907,7 @@
         <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -12937,10 +12925,10 @@
         <v>0</v>
       </c>
       <c r="AH93" t="n">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="AI93" t="n">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="AJ93" t="n">
         <v>335</v>
@@ -13008,16 +12996,16 @@
         <v>198</v>
       </c>
       <c r="M94" t="n">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="N94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
@@ -13029,7 +13017,7 @@
         <v>1</v>
       </c>
       <c r="T94" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="U94" t="n">
         <v>0</v>
@@ -13038,22 +13026,22 @@
         <v>408</v>
       </c>
       <c r="W94" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="X94" t="n">
         <v>198</v>
       </c>
       <c r="Y94" t="n">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="Z94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -13065,7 +13053,7 @@
         <v>1</v>
       </c>
       <c r="AF94" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -13074,7 +13062,7 @@
         <v>408</v>
       </c>
       <c r="AI94" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AJ94" t="n">
         <v>373</v>
@@ -13139,19 +13127,19 @@
         <v>303.54</v>
       </c>
       <c r="L95" t="n">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="M95" t="n">
-        <v>262</v>
+        <v>287</v>
       </c>
       <c r="N95" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -13169,25 +13157,25 @@
         <v>0</v>
       </c>
       <c r="V95" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="W95" t="n">
-        <v>306</v>
+        <v>328</v>
       </c>
       <c r="X95" t="n">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="Y95" t="n">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="Z95" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AA95" t="n">
         <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -13205,10 +13193,10 @@
         <v>0</v>
       </c>
       <c r="AH95" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AI95" t="n">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="AJ95" t="n">
         <v>356</v>
@@ -13273,19 +13261,19 @@
         <v>251.72</v>
       </c>
       <c r="L96" t="n">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="M96" t="n">
-        <v>188</v>
+        <v>260</v>
       </c>
       <c r="N96" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
@@ -13303,25 +13291,25 @@
         <v>0</v>
       </c>
       <c r="V96" t="n">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W96" t="n">
-        <v>289</v>
+        <v>312</v>
       </c>
       <c r="X96" t="n">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="Y96" t="n">
-        <v>188</v>
+        <v>260</v>
       </c>
       <c r="Z96" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -13339,10 +13327,10 @@
         <v>0</v>
       </c>
       <c r="AH96" t="n">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="AI96" t="n">
-        <v>289</v>
+        <v>312</v>
       </c>
       <c r="AJ96" t="n">
         <v>282</v>
@@ -13407,49 +13395,49 @@
         <v>258.16</v>
       </c>
       <c r="L97" t="n">
-        <v>143</v>
+        <v>115</v>
       </c>
       <c r="M97" t="n">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="N97" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="O97" t="n">
         <v>44</v>
       </c>
       <c r="P97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
       </c>
       <c r="T97" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="U97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V97" t="n">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="W97" t="n">
-        <v>207</v>
+        <v>240</v>
       </c>
       <c r="X97" t="n">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="Y97" t="n">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="Z97" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="AA97" t="n">
         <v>44</v>
@@ -13461,22 +13449,22 @@
         <v>0</v>
       </c>
       <c r="AD97" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE97" t="n">
         <v>0</v>
       </c>
       <c r="AF97" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AG97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH97" t="n">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="AI97" t="n">
-        <v>216</v>
+        <v>240</v>
       </c>
       <c r="AJ97" t="n">
         <v>378</v>
@@ -13541,19 +13529,19 @@
         <v>155.29</v>
       </c>
       <c r="L98" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="M98" t="n">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="N98" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O98" t="n">
         <v>9</v>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
@@ -13574,22 +13562,22 @@
         <v>399</v>
       </c>
       <c r="W98" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="X98" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Y98" t="n">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="Z98" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AA98" t="n">
         <v>9</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -13610,7 +13598,7 @@
         <v>399</v>
       </c>
       <c r="AI98" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AJ98" t="n">
         <v>367</v>
@@ -13675,10 +13663,10 @@
         <v>391.05</v>
       </c>
       <c r="L99" t="n">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="M99" t="n">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="N99" t="n">
         <v>0</v>
@@ -13687,7 +13675,7 @@
         <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -13705,16 +13693,16 @@
         <v>2</v>
       </c>
       <c r="V99" t="n">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="W99" t="n">
-        <v>280</v>
+        <v>297</v>
       </c>
       <c r="X99" t="n">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="Y99" t="n">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="Z99" t="n">
         <v>0</v>
@@ -13723,7 +13711,7 @@
         <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -13741,10 +13729,10 @@
         <v>2</v>
       </c>
       <c r="AH99" t="n">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="AI99" t="n">
-        <v>280</v>
+        <v>297</v>
       </c>
       <c r="AJ99" t="n">
         <v>321</v>
@@ -13809,19 +13797,19 @@
         <v>124.58</v>
       </c>
       <c r="L100" t="n">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="M100" t="n">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="N100" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
@@ -13833,31 +13821,31 @@
         <v>0</v>
       </c>
       <c r="T100" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="U100" t="n">
         <v>0</v>
       </c>
       <c r="V100" t="n">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="W100" t="n">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="X100" t="n">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="Y100" t="n">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="Z100" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AA100" t="n">
         <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -13869,16 +13857,16 @@
         <v>0</v>
       </c>
       <c r="AF100" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AG100" t="n">
         <v>0</v>
       </c>
       <c r="AH100" t="n">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="AI100" t="n">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="AJ100" t="n">
         <v>343</v>
@@ -13943,58 +13931,58 @@
         <v>171.75</v>
       </c>
       <c r="L101" t="n">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="M101" t="n">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
       </c>
       <c r="P101" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q101" t="n">
+        <v>0</v>
+      </c>
+      <c r="R101" t="n">
+        <v>1</v>
+      </c>
+      <c r="S101" t="n">
+        <v>0</v>
+      </c>
+      <c r="T101" t="n">
+        <v>84</v>
+      </c>
+      <c r="U101" t="n">
+        <v>1</v>
+      </c>
+      <c r="V101" t="n">
+        <v>509</v>
+      </c>
+      <c r="W101" t="n">
+        <v>311</v>
+      </c>
+      <c r="X101" t="n">
+        <v>199</v>
+      </c>
+      <c r="Y101" t="n">
+        <v>219</v>
+      </c>
+      <c r="Z101" t="n">
         <v>2</v>
       </c>
-      <c r="R101" t="n">
-        <v>1</v>
-      </c>
-      <c r="S101" t="n">
-        <v>0</v>
-      </c>
-      <c r="T101" t="n">
-        <v>82</v>
-      </c>
-      <c r="U101" t="n">
-        <v>1</v>
-      </c>
-      <c r="V101" t="n">
-        <v>502</v>
-      </c>
-      <c r="W101" t="n">
-        <v>290</v>
-      </c>
-      <c r="X101" t="n">
-        <v>212</v>
-      </c>
-      <c r="Y101" t="n">
-        <v>203</v>
-      </c>
-      <c r="Z101" t="n">
-        <v>0</v>
-      </c>
       <c r="AA101" t="n">
         <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC101" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD101" t="n">
         <v>1</v>
@@ -14003,16 +13991,16 @@
         <v>0</v>
       </c>
       <c r="AF101" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AG101" t="n">
         <v>1</v>
       </c>
       <c r="AH101" t="n">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="AI101" t="n">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="AJ101" t="n">
         <v>455</v>
@@ -14077,13 +14065,13 @@
         <v>343.73</v>
       </c>
       <c r="L102" t="n">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="M102" t="n">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="N102" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="O102" t="n">
         <v>5</v>
@@ -14107,19 +14095,19 @@
         <v>2</v>
       </c>
       <c r="V102" t="n">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="W102" t="n">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="X102" t="n">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="Y102" t="n">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="Z102" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AA102" t="n">
         <v>5</v>
@@ -14143,10 +14131,10 @@
         <v>2</v>
       </c>
       <c r="AH102" t="n">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AI102" t="n">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="AJ102" t="n">
         <v>472</v>
@@ -14211,10 +14199,10 @@
         <v>133.82</v>
       </c>
       <c r="L103" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="M103" t="n">
-        <v>322</v>
+        <v>352</v>
       </c>
       <c r="N103" t="n">
         <v>0</v>
@@ -14223,7 +14211,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="n">
         <v>0</v>
@@ -14241,25 +14229,25 @@
         <v>1</v>
       </c>
       <c r="V103" t="n">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="W103" t="n">
-        <v>375</v>
+        <v>399</v>
       </c>
       <c r="X103" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="Y103" t="n">
-        <v>322</v>
+        <v>349</v>
       </c>
       <c r="Z103" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA103" t="n">
         <v>1</v>
       </c>
       <c r="AB103" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -14277,10 +14265,10 @@
         <v>1</v>
       </c>
       <c r="AH103" t="n">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="AI103" t="n">
-        <v>375</v>
+        <v>399</v>
       </c>
       <c r="AJ103" t="n">
         <v>316</v>
@@ -14345,19 +14333,19 @@
         <v>446.53</v>
       </c>
       <c r="L104" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M104" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N104" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="O104" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="P104" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Q104" t="n">
         <v>0</v>
@@ -14375,25 +14363,25 @@
         <v>3</v>
       </c>
       <c r="V104" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="W104" t="n">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="X104" t="n">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="Y104" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Z104" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="AA104" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AB104" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -14411,10 +14399,10 @@
         <v>3</v>
       </c>
       <c r="AH104" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="AI104" t="n">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="AJ104" t="n">
         <v>422</v>
@@ -14479,16 +14467,16 @@
         <v>272.86</v>
       </c>
       <c r="L105" t="n">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="M105" t="n">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="N105" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="O105" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="P105" t="n">
         <v>0</v>
@@ -14509,22 +14497,22 @@
         <v>0</v>
       </c>
       <c r="V105" t="n">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="W105" t="n">
-        <v>294</v>
+        <v>319</v>
       </c>
       <c r="X105" t="n">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="Y105" t="n">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="Z105" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="AA105" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AB105" t="n">
         <v>0</v>
@@ -14545,10 +14533,10 @@
         <v>0</v>
       </c>
       <c r="AH105" t="n">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="AI105" t="n">
-        <v>294</v>
+        <v>319</v>
       </c>
       <c r="AJ105" t="n">
         <v>391</v>
@@ -14613,10 +14601,10 @@
         <v>381.59</v>
       </c>
       <c r="L106" t="n">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="M106" t="n">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="N106" t="n">
         <v>0</v>
@@ -14625,7 +14613,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q106" t="n">
         <v>0</v>
@@ -14637,22 +14625,22 @@
         <v>0</v>
       </c>
       <c r="T106" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="U106" t="n">
         <v>0</v>
       </c>
       <c r="V106" t="n">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="W106" t="n">
-        <v>321</v>
+        <v>337</v>
       </c>
       <c r="X106" t="n">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="Y106" t="n">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="Z106" t="n">
         <v>0</v>
@@ -14661,7 +14649,7 @@
         <v>1</v>
       </c>
       <c r="AB106" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -14673,16 +14661,16 @@
         <v>0</v>
       </c>
       <c r="AF106" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AG106" t="n">
         <v>0</v>
       </c>
       <c r="AH106" t="n">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="AI106" t="n">
-        <v>321</v>
+        <v>337</v>
       </c>
       <c r="AJ106" t="n">
         <v>366</v>
@@ -14747,13 +14735,13 @@
         <v>456.24</v>
       </c>
       <c r="L107" t="n">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="M107" t="n">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="N107" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14780,16 +14768,16 @@
         <v>367</v>
       </c>
       <c r="W107" t="n">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="X107" t="n">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="Y107" t="n">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="Z107" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14816,7 +14804,7 @@
         <v>367</v>
       </c>
       <c r="AI107" t="n">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="AJ107" t="n">
         <v>322</v>
@@ -14881,19 +14869,19 @@
         <v>422.75</v>
       </c>
       <c r="L108" t="n">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="M108" t="n">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="N108" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
       </c>
       <c r="P108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q108" t="n">
         <v>0</v>
@@ -14914,22 +14902,22 @@
         <v>382</v>
       </c>
       <c r="W108" t="n">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="X108" t="n">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="Y108" t="n">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="Z108" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
       </c>
       <c r="AB108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -14950,7 +14938,7 @@
         <v>382</v>
       </c>
       <c r="AI108" t="n">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="AJ108" t="n">
         <v>324</v>
@@ -15015,19 +15003,19 @@
         <v>163.92</v>
       </c>
       <c r="L109" t="n">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="M109" t="n">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="N109" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
       </c>
       <c r="P109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q109" t="n">
         <v>0</v>
@@ -15039,31 +15027,31 @@
         <v>0</v>
       </c>
       <c r="T109" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="U109" t="n">
         <v>1</v>
       </c>
       <c r="V109" t="n">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="W109" t="n">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="X109" t="n">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="Y109" t="n">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="Z109" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
       </c>
       <c r="AB109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -15075,16 +15063,16 @@
         <v>0</v>
       </c>
       <c r="AF109" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="AG109" t="n">
         <v>1</v>
       </c>
       <c r="AH109" t="n">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="AI109" t="n">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="AJ109" t="n">
         <v>407</v>
@@ -15149,19 +15137,19 @@
         <v>383.55</v>
       </c>
       <c r="L110" t="n">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="M110" t="n">
-        <v>352</v>
+        <v>370</v>
       </c>
       <c r="N110" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>5</v>
       </c>
       <c r="P110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q110" t="n">
         <v>0</v>
@@ -15176,28 +15164,28 @@
         <v>20</v>
       </c>
       <c r="U110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V110" t="n">
         <v>622</v>
       </c>
       <c r="W110" t="n">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="X110" t="n">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="Y110" t="n">
-        <v>352</v>
+        <v>370</v>
       </c>
       <c r="Z110" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AA110" t="n">
         <v>5</v>
       </c>
       <c r="AB110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -15212,13 +15200,13 @@
         <v>20</v>
       </c>
       <c r="AG110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH110" t="n">
         <v>622</v>
       </c>
       <c r="AI110" t="n">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="AJ110" t="n">
         <v>507</v>
@@ -15283,13 +15271,13 @@
         <v>209.85</v>
       </c>
       <c r="L111" t="n">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="M111" t="n">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="N111" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O111" t="n">
         <v>2</v>
@@ -15313,19 +15301,19 @@
         <v>0</v>
       </c>
       <c r="V111" t="n">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="W111" t="n">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="X111" t="n">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="Y111" t="n">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="Z111" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA111" t="n">
         <v>2</v>
@@ -15349,10 +15337,10 @@
         <v>0</v>
       </c>
       <c r="AH111" t="n">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="AI111" t="n">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="AJ111" t="n">
         <v>294</v>
@@ -15417,10 +15405,10 @@
         <v>87.28</v>
       </c>
       <c r="L112" t="n">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="M112" t="n">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="N112" t="n">
         <v>0</v>
@@ -15441,22 +15429,22 @@
         <v>0</v>
       </c>
       <c r="T112" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="U112" t="n">
         <v>0</v>
       </c>
       <c r="V112" t="n">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="W112" t="n">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="X112" t="n">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="Y112" t="n">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="Z112" t="n">
         <v>0</v>
@@ -15477,16 +15465,16 @@
         <v>0</v>
       </c>
       <c r="AF112" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AG112" t="n">
         <v>0</v>
       </c>
       <c r="AH112" t="n">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="AI112" t="n">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="AJ112" t="n">
         <v>403</v>
@@ -15551,19 +15539,19 @@
         <v>178.52</v>
       </c>
       <c r="L113" t="n">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="M113" t="n">
-        <v>194</v>
+        <v>278</v>
       </c>
       <c r="N113" t="n">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
       </c>
       <c r="P113" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="Q113" t="n">
         <v>0</v>
@@ -15575,31 +15563,31 @@
         <v>0</v>
       </c>
       <c r="T113" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="U113" t="n">
         <v>0</v>
       </c>
       <c r="V113" t="n">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="W113" t="n">
-        <v>337</v>
+        <v>359</v>
       </c>
       <c r="X113" t="n">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="Y113" t="n">
-        <v>194</v>
+        <v>278</v>
       </c>
       <c r="Z113" t="n">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="AA113" t="n">
         <v>0</v>
       </c>
       <c r="AB113" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="AC113" t="n">
         <v>0</v>
@@ -15611,16 +15599,16 @@
         <v>0</v>
       </c>
       <c r="AF113" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AG113" t="n">
         <v>0</v>
       </c>
       <c r="AH113" t="n">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="AI113" t="n">
-        <v>337</v>
+        <v>359</v>
       </c>
       <c r="AJ113" t="n">
         <v>362</v>
@@ -15688,10 +15676,10 @@
         <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="N114" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15709,7 +15697,7 @@
         <v>0</v>
       </c>
       <c r="T114" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="U114" t="n">
         <v>4</v>
@@ -15724,10 +15712,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="Z114" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15745,7 +15733,7 @@
         <v>0</v>
       </c>
       <c r="AF114" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AG114" t="n">
         <v>4</v>
@@ -15822,7 +15810,7 @@
         <v>212</v>
       </c>
       <c r="M115" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="N115" t="n">
         <v>6</v>
@@ -15843,7 +15831,7 @@
         <v>0</v>
       </c>
       <c r="T115" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="U115" t="n">
         <v>0</v>
@@ -15858,7 +15846,7 @@
         <v>212</v>
       </c>
       <c r="Y115" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="Z115" t="n">
         <v>6</v>
@@ -15879,7 +15867,7 @@
         <v>0</v>
       </c>
       <c r="AF115" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG115" t="n">
         <v>0</v>
@@ -15953,13 +15941,13 @@
         <v>249.48</v>
       </c>
       <c r="L116" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="M116" t="n">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="N116" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15983,19 +15971,19 @@
         <v>1</v>
       </c>
       <c r="V116" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="W116" t="n">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="X116" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="Y116" t="n">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="Z116" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA116" t="n">
         <v>0</v>
@@ -16019,10 +16007,10 @@
         <v>1</v>
       </c>
       <c r="AH116" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="AI116" t="n">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="AJ116" t="n">
         <v>333</v>
@@ -16087,19 +16075,19 @@
         <v>340.03</v>
       </c>
       <c r="L117" t="n">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="M117" t="n">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="N117" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
       </c>
       <c r="P117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q117" t="n">
         <v>0</v>
@@ -16111,31 +16099,31 @@
         <v>0</v>
       </c>
       <c r="T117" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="U117" t="n">
         <v>0</v>
       </c>
       <c r="V117" t="n">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="W117" t="n">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="X117" t="n">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="Y117" t="n">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="Z117" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AA117" t="n">
         <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -16147,16 +16135,16 @@
         <v>0</v>
       </c>
       <c r="AF117" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AG117" t="n">
         <v>0</v>
       </c>
       <c r="AH117" t="n">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AI117" t="n">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="AJ117" t="n">
         <v>364</v>
@@ -16221,16 +16209,16 @@
         <v>362.14</v>
       </c>
       <c r="L118" t="n">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="M118" t="n">
-        <v>220</v>
+        <v>244</v>
       </c>
       <c r="N118" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O118" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P118" t="n">
         <v>0</v>
@@ -16251,22 +16239,22 @@
         <v>0</v>
       </c>
       <c r="V118" t="n">
-        <v>485</v>
+        <v>501</v>
       </c>
       <c r="W118" t="n">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="X118" t="n">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="Y118" t="n">
-        <v>220</v>
+        <v>244</v>
       </c>
       <c r="Z118" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AA118" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB118" t="n">
         <v>0</v>
@@ -16287,10 +16275,10 @@
         <v>0</v>
       </c>
       <c r="AH118" t="n">
-        <v>485</v>
+        <v>501</v>
       </c>
       <c r="AI118" t="n">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="AJ118" t="n">
         <v>378</v>
@@ -16355,13 +16343,13 @@
         <v>339.34</v>
       </c>
       <c r="L119" t="n">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="M119" t="n">
-        <v>195</v>
+        <v>318</v>
       </c>
       <c r="N119" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -16385,19 +16373,19 @@
         <v>3</v>
       </c>
       <c r="V119" t="n">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="W119" t="n">
-        <v>358</v>
+        <v>375</v>
       </c>
       <c r="X119" t="n">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="Y119" t="n">
-        <v>195</v>
+        <v>318</v>
       </c>
       <c r="Z119" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -16421,10 +16409,10 @@
         <v>3</v>
       </c>
       <c r="AH119" t="n">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AI119" t="n">
-        <v>358</v>
+        <v>375</v>
       </c>
       <c r="AJ119" t="n">
         <v>420</v>
@@ -16489,76 +16477,76 @@
         <v>210.63</v>
       </c>
       <c r="L120" t="n">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="M120" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N120" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O120" t="n">
+        <v>2</v>
+      </c>
+      <c r="P120" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0</v>
+      </c>
+      <c r="R120" t="n">
         <v>3</v>
       </c>
-      <c r="P120" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q120" t="n">
+      <c r="S120" t="n">
+        <v>0</v>
+      </c>
+      <c r="T120" t="n">
+        <v>80</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0</v>
+      </c>
+      <c r="V120" t="n">
+        <v>511</v>
+      </c>
+      <c r="W120" t="n">
+        <v>273</v>
+      </c>
+      <c r="X120" t="n">
+        <v>236</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>181</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA120" t="n">
         <v>2</v>
       </c>
-      <c r="R120" t="n">
-        <v>2</v>
-      </c>
-      <c r="S120" t="n">
-        <v>0</v>
-      </c>
-      <c r="T120" t="n">
-        <v>56</v>
-      </c>
-      <c r="U120" t="n">
-        <v>0</v>
-      </c>
-      <c r="V120" t="n">
-        <v>509</v>
-      </c>
-      <c r="W120" t="n">
-        <v>250</v>
-      </c>
-      <c r="X120" t="n">
-        <v>254</v>
-      </c>
-      <c r="Y120" t="n">
-        <v>169</v>
-      </c>
-      <c r="Z120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA120" t="n">
+      <c r="AB120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD120" t="n">
         <v>3</v>
       </c>
-      <c r="AB120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC120" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD120" t="n">
-        <v>2</v>
-      </c>
       <c r="AE120" t="n">
         <v>0</v>
       </c>
       <c r="AF120" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG120" t="n">
         <v>0</v>
       </c>
       <c r="AH120" t="n">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AI120" t="n">
-        <v>252</v>
+        <v>273</v>
       </c>
       <c r="AJ120" t="n">
         <v>430</v>
@@ -16623,19 +16611,19 @@
         <v>167.75</v>
       </c>
       <c r="L121" t="n">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="M121" t="n">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="N121" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O121" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q121" t="n">
         <v>0</v>
@@ -16647,31 +16635,31 @@
         <v>0</v>
       </c>
       <c r="T121" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="U121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V121" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="W121" t="n">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="X121" t="n">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="Y121" t="n">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="Z121" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA121" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -16683,16 +16671,16 @@
         <v>0</v>
       </c>
       <c r="AF121" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="AG121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH121" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AI121" t="n">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="AJ121" t="n">
         <v>379</v>
@@ -16757,10 +16745,10 @@
         <v>149.78</v>
       </c>
       <c r="L122" t="n">
-        <v>223</v>
+        <v>202</v>
       </c>
       <c r="M122" t="n">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="N122" t="n">
         <v>2</v>
@@ -16769,7 +16757,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q122" t="n">
         <v>0</v>
@@ -16787,16 +16775,16 @@
         <v>0</v>
       </c>
       <c r="V122" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="W122" t="n">
-        <v>241</v>
+        <v>263</v>
       </c>
       <c r="X122" t="n">
-        <v>223</v>
+        <v>202</v>
       </c>
       <c r="Y122" t="n">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="Z122" t="n">
         <v>2</v>
@@ -16805,7 +16793,7 @@
         <v>1</v>
       </c>
       <c r="AB122" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -16823,10 +16811,10 @@
         <v>0</v>
       </c>
       <c r="AH122" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AI122" t="n">
-        <v>241</v>
+        <v>263</v>
       </c>
       <c r="AJ122" t="n">
         <v>419</v>
@@ -16891,13 +16879,13 @@
         <v>400.39</v>
       </c>
       <c r="L123" t="n">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="M123" t="n">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="N123" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O123" t="n">
         <v>5</v>
@@ -16906,7 +16894,7 @@
         <v>1</v>
       </c>
       <c r="Q123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R123" t="n">
         <v>0</v>
@@ -16924,16 +16912,16 @@
         <v>493</v>
       </c>
       <c r="W123" t="n">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="X123" t="n">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="Y123" t="n">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="Z123" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA123" t="n">
         <v>5</v>
@@ -16942,7 +16930,7 @@
         <v>1</v>
       </c>
       <c r="AC123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD123" t="n">
         <v>0</v>
@@ -16960,7 +16948,7 @@
         <v>493</v>
       </c>
       <c r="AI123" t="n">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="AJ123" t="n">
         <v>432</v>
@@ -17025,13 +17013,13 @@
         <v>218.94</v>
       </c>
       <c r="L124" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="M124" t="n">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="N124" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>4</v>
@@ -17055,19 +17043,19 @@
         <v>1</v>
       </c>
       <c r="V124" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="W124" t="n">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="X124" t="n">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="Y124" t="n">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="Z124" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA124" t="n">
         <v>4</v>
@@ -17091,10 +17079,10 @@
         <v>1</v>
       </c>
       <c r="AH124" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AI124" t="n">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="AJ124" t="n">
         <v>437</v>
@@ -17159,19 +17147,19 @@
         <v>234.31</v>
       </c>
       <c r="L125" t="n">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="M125" t="n">
-        <v>128</v>
+        <v>225</v>
       </c>
       <c r="N125" t="n">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
       </c>
       <c r="P125" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q125" t="n">
         <v>0</v>
@@ -17189,25 +17177,25 @@
         <v>2</v>
       </c>
       <c r="V125" t="n">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="W125" t="n">
-        <v>266</v>
+        <v>319</v>
       </c>
       <c r="X125" t="n">
-        <v>93</v>
+        <v>45</v>
       </c>
       <c r="Y125" t="n">
-        <v>128</v>
+        <v>225</v>
       </c>
       <c r="Z125" t="n">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="AA125" t="n">
         <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -17225,10 +17213,10 @@
         <v>2</v>
       </c>
       <c r="AH125" t="n">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="AI125" t="n">
-        <v>265</v>
+        <v>319</v>
       </c>
       <c r="AJ125" t="n">
         <v>303</v>
@@ -17293,10 +17281,10 @@
         <v>222.05</v>
       </c>
       <c r="L126" t="n">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="M126" t="n">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="N126" t="n">
         <v>0</v>
@@ -17317,25 +17305,25 @@
         <v>0</v>
       </c>
       <c r="T126" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="U126" t="n">
         <v>0</v>
       </c>
       <c r="V126" t="n">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="W126" t="n">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="X126" t="n">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="Y126" t="n">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="Z126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA126" t="n">
         <v>0</v>
@@ -17353,16 +17341,16 @@
         <v>0</v>
       </c>
       <c r="AF126" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="AG126" t="n">
         <v>0</v>
       </c>
       <c r="AH126" t="n">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="AI126" t="n">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="AJ126" t="n">
         <v>366</v>
@@ -17427,16 +17415,16 @@
         <v>249.95</v>
       </c>
       <c r="L127" t="n">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="M127" t="n">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O127" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="P127" t="n">
         <v>2</v>
@@ -17457,22 +17445,22 @@
         <v>0</v>
       </c>
       <c r="V127" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="W127" t="n">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="X127" t="n">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="Y127" t="n">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="Z127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA127" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AB127" t="n">
         <v>2</v>
@@ -17493,10 +17481,10 @@
         <v>0</v>
       </c>
       <c r="AH127" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AI127" t="n">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="AJ127" t="n">
         <v>394</v>
@@ -17564,13 +17552,13 @@
         <v>180</v>
       </c>
       <c r="M128" t="n">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="N128" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="O128" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="P128" t="n">
         <v>2</v>
@@ -17585,7 +17573,7 @@
         <v>0</v>
       </c>
       <c r="T128" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U128" t="n">
         <v>0</v>
@@ -17594,19 +17582,19 @@
         <v>470</v>
       </c>
       <c r="W128" t="n">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="X128" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y128" t="n">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="Z128" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="AA128" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AB128" t="n">
         <v>2</v>
@@ -17621,7 +17609,7 @@
         <v>0</v>
       </c>
       <c r="AF128" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AG128" t="n">
         <v>0</v>
@@ -17630,7 +17618,7 @@
         <v>470</v>
       </c>
       <c r="AI128" t="n">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="AJ128" t="n">
         <v>372</v>
@@ -17695,13 +17683,13 @@
         <v>183.91</v>
       </c>
       <c r="L129" t="n">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="M129" t="n">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -17728,16 +17716,16 @@
         <v>345</v>
       </c>
       <c r="W129" t="n">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="X129" t="n">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="Y129" t="n">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="Z129" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA129" t="n">
         <v>0</v>
@@ -17764,7 +17752,7 @@
         <v>345</v>
       </c>
       <c r="AI129" t="n">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="AJ129" t="n">
         <v>313</v>
@@ -17829,19 +17817,19 @@
         <v>217.83</v>
       </c>
       <c r="L130" t="n">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="M130" t="n">
-        <v>160</v>
+        <v>259</v>
       </c>
       <c r="N130" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q130" t="n">
         <v>0</v>
@@ -17859,25 +17847,25 @@
         <v>0</v>
       </c>
       <c r="V130" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="W130" t="n">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="X130" t="n">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="Y130" t="n">
-        <v>160</v>
+        <v>259</v>
       </c>
       <c r="Z130" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AB130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -17895,10 +17883,10 @@
         <v>0</v>
       </c>
       <c r="AH130" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AI130" t="n">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="AJ130" t="n">
         <v>386</v>
@@ -17963,13 +17951,13 @@
         <v>257.89</v>
       </c>
       <c r="L131" t="n">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="M131" t="n">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="N131" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
         <v>1</v>
@@ -17987,7 +17975,7 @@
         <v>0</v>
       </c>
       <c r="T131" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="U131" t="n">
         <v>0</v>
@@ -17996,16 +17984,16 @@
         <v>399</v>
       </c>
       <c r="W131" t="n">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="X131" t="n">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="Y131" t="n">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="Z131" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA131" t="n">
         <v>1</v>
@@ -18023,7 +18011,7 @@
         <v>0</v>
       </c>
       <c r="AF131" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="AG131" t="n">
         <v>0</v>
@@ -18032,7 +18020,7 @@
         <v>399</v>
       </c>
       <c r="AI131" t="n">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="AJ131" t="n">
         <v>370</v>
@@ -18097,13 +18085,13 @@
         <v>140.52</v>
       </c>
       <c r="L132" t="n">
+        <v>182</v>
+      </c>
+      <c r="M132" t="n">
         <v>188</v>
       </c>
-      <c r="M132" t="n">
-        <v>189</v>
-      </c>
       <c r="N132" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -18121,25 +18109,25 @@
         <v>0</v>
       </c>
       <c r="T132" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="U132" t="n">
         <v>1</v>
       </c>
       <c r="V132" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="W132" t="n">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="X132" t="n">
+        <v>182</v>
+      </c>
+      <c r="Y132" t="n">
         <v>188</v>
       </c>
-      <c r="Y132" t="n">
-        <v>189</v>
-      </c>
       <c r="Z132" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AA132" t="n">
         <v>0</v>
@@ -18157,16 +18145,16 @@
         <v>0</v>
       </c>
       <c r="AF132" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AG132" t="n">
         <v>1</v>
       </c>
       <c r="AH132" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AI132" t="n">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="AJ132" t="n">
         <v>368</v>

--- a/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_PCL_PROPORSI USAHA.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_PCL_PROPORSI USAHA.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,202 +429,202 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Nama PCL</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Email PCL</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Nama PML</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Email PML</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>nama_kec</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>koseka</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Usaha (semua status keberadaan usaha)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Usaha BKU</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Persentase Usaha BKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Usaha Dalam Keluarga</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Persentase Usaha Dalam Keluarga</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>DRAFT</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>APPROVED BY Pengawas</t>
         </is>

--- a/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_PCL_PROPORSI USAHA.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_PCL_PROPORSI USAHA.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,206 +413,206 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN132"/>
+  <dimension ref="A1:AN133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Nama PCL</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Email PCL</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Nama PML</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Email PML</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>nama_kec</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>koseka</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Jumlah Usaha (semua status keberadaan usaha)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Jumlah Usaha BKU</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Persentase Usaha BKU</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Jumlah Usaha Dalam Keluarga</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Persentase Usaha Dalam Keluarga</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>DRAFT</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>APPROVED BY Pengawas</t>
         </is>
@@ -749,19 +737,19 @@
         <v>447</v>
       </c>
       <c r="AJ2" t="n">
-        <v>364</v>
+        <v>64</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AL2" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="AM2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>4</v>
+        <v>329</v>
       </c>
     </row>
     <row r="3">
@@ -1017,7 +1005,7 @@
         <v>342</v>
       </c>
       <c r="AJ4" t="n">
-        <v>363</v>
+        <v>94</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
@@ -1029,7 +1017,7 @@
         <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>310</v>
       </c>
     </row>
     <row r="5">
@@ -1151,7 +1139,7 @@
         <v>249</v>
       </c>
       <c r="AJ5" t="n">
-        <v>384</v>
+        <v>184</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
@@ -1160,10 +1148,10 @@
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
     </row>
     <row r="6">
@@ -1285,7 +1273,7 @@
         <v>233</v>
       </c>
       <c r="AJ6" t="n">
-        <v>354</v>
+        <v>166</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
@@ -1297,7 +1285,7 @@
         <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>209</v>
       </c>
     </row>
     <row r="7">
@@ -1419,19 +1407,19 @@
         <v>395</v>
       </c>
       <c r="AJ7" t="n">
-        <v>336</v>
+        <v>27</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>326</v>
       </c>
     </row>
     <row r="8">
@@ -1553,19 +1541,19 @@
         <v>285</v>
       </c>
       <c r="AJ8" t="n">
-        <v>304</v>
+        <v>85</v>
       </c>
       <c r="AK8" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AL8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
         <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9">
@@ -1687,19 +1675,19 @@
         <v>389</v>
       </c>
       <c r="AJ9" t="n">
-        <v>288</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10">
@@ -1821,19 +1809,19 @@
         <v>278</v>
       </c>
       <c r="AJ10" t="n">
-        <v>324</v>
+        <v>141</v>
       </c>
       <c r="AK10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1955,19 +1943,19 @@
         <v>271</v>
       </c>
       <c r="AJ11" t="n">
-        <v>373</v>
+        <v>142</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AN11" t="n">
-        <v>2</v>
+        <v>220</v>
       </c>
     </row>
     <row r="12">
@@ -2089,19 +2077,19 @@
         <v>386</v>
       </c>
       <c r="AJ12" t="n">
-        <v>383</v>
+        <v>104</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
         <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>1</v>
+        <v>350</v>
       </c>
     </row>
     <row r="13">
@@ -2223,19 +2211,19 @@
         <v>493</v>
       </c>
       <c r="AJ13" t="n">
-        <v>373</v>
+        <v>75</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AM13" t="n">
         <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>448</v>
       </c>
     </row>
     <row r="14">
@@ -2357,19 +2345,19 @@
         <v>347</v>
       </c>
       <c r="AJ14" t="n">
-        <v>364</v>
+        <v>74</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AL14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>3</v>
+        <v>298</v>
       </c>
     </row>
     <row r="15">
@@ -2491,19 +2479,19 @@
         <v>308</v>
       </c>
       <c r="AJ15" t="n">
-        <v>324</v>
+        <v>156</v>
       </c>
       <c r="AK15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AL15" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="AM15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>263</v>
       </c>
     </row>
     <row r="16">
@@ -2625,19 +2613,19 @@
         <v>382</v>
       </c>
       <c r="AJ16" t="n">
-        <v>288</v>
+        <v>40</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>344</v>
       </c>
     </row>
     <row r="17">
@@ -2672,7 +2660,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1720</v>
+        <v>2180</v>
       </c>
       <c r="H17" t="n">
         <v>330</v>
@@ -2681,16 +2669,16 @@
         <v>76.98999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>1020</v>
+        <v>1350</v>
       </c>
       <c r="K17" t="n">
-        <v>241.74</v>
+        <v>313.48</v>
       </c>
       <c r="L17" t="n">
         <v>71</v>
       </c>
       <c r="M17" t="n">
-        <v>382</v>
+        <v>410</v>
       </c>
       <c r="N17" t="n">
         <v>2</v>
@@ -2711,22 +2699,22 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>494</v>
+        <v>529</v>
       </c>
       <c r="W17" t="n">
-        <v>414</v>
+        <v>449</v>
       </c>
       <c r="X17" t="n">
         <v>71</v>
       </c>
       <c r="Y17" t="n">
-        <v>382</v>
+        <v>410</v>
       </c>
       <c r="Z17" t="n">
         <v>2</v>
@@ -2747,31 +2735,31 @@
         <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>494</v>
+        <v>529</v>
       </c>
       <c r="AI17" t="n">
-        <v>414</v>
+        <v>449</v>
       </c>
       <c r="AJ17" t="n">
-        <v>370</v>
+        <v>71</v>
       </c>
       <c r="AK17" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AL17" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AN17" t="n">
-        <v>1</v>
+        <v>410</v>
       </c>
     </row>
     <row r="18">
@@ -2893,19 +2881,19 @@
         <v>377</v>
       </c>
       <c r="AJ18" t="n">
-        <v>366</v>
+        <v>45</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL18" t="n">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AN18" t="n">
-        <v>3</v>
+        <v>277</v>
       </c>
     </row>
     <row r="19">
@@ -3027,19 +3015,19 @@
         <v>318</v>
       </c>
       <c r="AJ19" t="n">
-        <v>423</v>
+        <v>150</v>
       </c>
       <c r="AK19" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
         <v>2</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>291</v>
       </c>
     </row>
     <row r="20">
@@ -3161,19 +3149,19 @@
         <v>307</v>
       </c>
       <c r="AJ20" t="n">
-        <v>284</v>
+        <v>15</v>
       </c>
       <c r="AK20" t="n">
         <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>239</v>
       </c>
     </row>
     <row r="21">
@@ -3295,19 +3283,19 @@
         <v>253</v>
       </c>
       <c r="AJ21" t="n">
-        <v>367</v>
+        <v>163</v>
       </c>
       <c r="AK21" t="n">
         <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AN21" t="n">
-        <v>4</v>
+        <v>213</v>
       </c>
     </row>
     <row r="22">
@@ -3342,34 +3330,34 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1670</v>
+        <v>1780</v>
       </c>
       <c r="H22" t="n">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="I22" t="n">
-        <v>44.13</v>
+        <v>16.35</v>
       </c>
       <c r="J22" t="n">
-        <v>960</v>
+        <v>1150</v>
       </c>
       <c r="K22" t="n">
-        <v>219.19</v>
+        <v>261.55</v>
       </c>
       <c r="L22" t="n">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="M22" t="n">
-        <v>321</v>
+        <v>299</v>
       </c>
       <c r="N22" t="n">
         <v>1</v>
       </c>
       <c r="O22" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="P22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3381,31 +3369,31 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>531</v>
+        <v>488</v>
       </c>
       <c r="W22" t="n">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="X22" t="n">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="Y22" t="n">
-        <v>321</v>
+        <v>299</v>
       </c>
       <c r="Z22" t="n">
         <v>1</v>
       </c>
       <c r="AA22" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="AB22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3417,31 +3405,31 @@
         <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>531</v>
+        <v>488</v>
       </c>
       <c r="AI22" t="n">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="AJ22" t="n">
-        <v>410</v>
+        <v>105</v>
       </c>
       <c r="AK22" t="n">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="AL22" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="AM22" t="n">
         <v>1</v>
       </c>
       <c r="AN22" t="n">
-        <v>22</v>
+        <v>299</v>
       </c>
     </row>
     <row r="23">
@@ -3563,19 +3551,19 @@
         <v>423</v>
       </c>
       <c r="AJ23" t="n">
-        <v>450</v>
+        <v>141</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL23" t="n">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="AM23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>354</v>
       </c>
     </row>
     <row r="24">
@@ -3697,19 +3685,19 @@
         <v>282</v>
       </c>
       <c r="AJ24" t="n">
-        <v>359</v>
+        <v>137</v>
       </c>
       <c r="AK24" t="n">
         <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>165</v>
       </c>
     </row>
     <row r="25">
@@ -3831,25 +3819,25 @@
         <v>368</v>
       </c>
       <c r="AJ25" t="n">
-        <v>308</v>
+        <v>32</v>
       </c>
       <c r="AK25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>4</v>
+        <v>297</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Jessica Juanita Lombontari</t>
+          <t>NaN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3878,34 +3866,34 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>3330</v>
+        <v>680</v>
       </c>
       <c r="H26" t="n">
-        <v>140</v>
+        <v>10</v>
       </c>
       <c r="I26" t="n">
-        <v>28.31</v>
+        <v>1.47</v>
       </c>
       <c r="J26" t="n">
-        <v>2220</v>
+        <v>490</v>
       </c>
       <c r="K26" t="n">
-        <v>467.24</v>
+        <v>72.06</v>
       </c>
       <c r="L26" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>211</v>
+        <v>50</v>
       </c>
       <c r="N26" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -3917,31 +3905,31 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="U26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V26" t="n">
-        <v>479</v>
+        <v>70</v>
       </c>
       <c r="W26" t="n">
-        <v>309</v>
+        <v>70</v>
       </c>
       <c r="X26" t="n">
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>211</v>
+        <v>50</v>
       </c>
       <c r="Z26" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3953,31 +3941,31 @@
         <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="AG26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH26" t="n">
-        <v>479</v>
+        <v>70</v>
       </c>
       <c r="AI26" t="n">
-        <v>307</v>
+        <v>70</v>
       </c>
       <c r="AJ26" t="n">
-        <v>419</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27">
@@ -4099,19 +4087,19 @@
         <v>387</v>
       </c>
       <c r="AJ27" t="n">
-        <v>342</v>
+        <v>56</v>
       </c>
       <c r="AK27" t="n">
         <v>0</v>
       </c>
       <c r="AL27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AM27" t="n">
         <v>0</v>
       </c>
       <c r="AN27" t="n">
-        <v>3</v>
+        <v>315</v>
       </c>
     </row>
     <row r="28">
@@ -4233,10 +4221,10 @@
         <v>375</v>
       </c>
       <c r="AJ28" t="n">
-        <v>384</v>
+        <v>109</v>
       </c>
       <c r="AK28" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4245,7 +4233,7 @@
         <v>0</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>318</v>
       </c>
     </row>
     <row r="29">
@@ -4367,19 +4355,19 @@
         <v>343</v>
       </c>
       <c r="AJ29" t="n">
-        <v>357</v>
+        <v>133</v>
       </c>
       <c r="AK29" t="n">
         <v>0</v>
       </c>
       <c r="AL29" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>266</v>
       </c>
     </row>
     <row r="30">
@@ -4501,19 +4489,19 @@
         <v>380</v>
       </c>
       <c r="AJ30" t="n">
-        <v>457</v>
+        <v>139</v>
       </c>
       <c r="AK30" t="n">
         <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AM30" t="n">
         <v>0</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="31">
@@ -4635,19 +4623,19 @@
         <v>201</v>
       </c>
       <c r="AJ31" t="n">
-        <v>315</v>
+        <v>3</v>
       </c>
       <c r="AK31" t="n">
-        <v>10</v>
+        <v>136</v>
       </c>
       <c r="AL31" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AM31" t="n">
         <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
     </row>
     <row r="32">
@@ -4769,19 +4757,19 @@
         <v>281</v>
       </c>
       <c r="AJ32" t="n">
-        <v>308</v>
+        <v>134</v>
       </c>
       <c r="AK32" t="n">
         <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
     </row>
     <row r="33">
@@ -4903,19 +4891,19 @@
         <v>282</v>
       </c>
       <c r="AJ33" t="n">
-        <v>365</v>
+        <v>156</v>
       </c>
       <c r="AK33" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AL33" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
     </row>
     <row r="34">
@@ -5037,19 +5025,19 @@
         <v>450</v>
       </c>
       <c r="AJ34" t="n">
-        <v>410</v>
+        <v>126</v>
       </c>
       <c r="AK34" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="AL34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AM34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>425</v>
       </c>
     </row>
     <row r="35">
@@ -5171,19 +5159,19 @@
         <v>243</v>
       </c>
       <c r="AJ35" t="n">
-        <v>303</v>
+        <v>131</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL35" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AM35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>214</v>
       </c>
     </row>
     <row r="36">
@@ -5305,19 +5293,19 @@
         <v>477</v>
       </c>
       <c r="AJ36" t="n">
-        <v>412</v>
+        <v>93</v>
       </c>
       <c r="AK36" t="n">
         <v>0</v>
       </c>
       <c r="AL36" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AM36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN36" t="n">
-        <v>4</v>
+        <v>325</v>
       </c>
     </row>
     <row r="37">
@@ -5439,19 +5427,19 @@
         <v>518</v>
       </c>
       <c r="AJ37" t="n">
-        <v>371</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="n">
         <v>0</v>
       </c>
       <c r="AL37" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AM37" t="n">
         <v>0</v>
       </c>
       <c r="AN37" t="n">
-        <v>0</v>
+        <v>432</v>
       </c>
     </row>
     <row r="38">
@@ -5482,7 +5470,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5573,19 +5561,19 @@
         <v>365</v>
       </c>
       <c r="AJ38" t="n">
-        <v>453</v>
+        <v>122</v>
       </c>
       <c r="AK38" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="AL38" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>296</v>
       </c>
     </row>
     <row r="39">
@@ -5616,7 +5604,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5707,19 +5695,19 @@
         <v>313</v>
       </c>
       <c r="AJ39" t="n">
-        <v>445</v>
+        <v>152</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AL39" t="n">
         <v>4</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AN39" t="n">
-        <v>0</v>
+        <v>237</v>
       </c>
     </row>
     <row r="40">
@@ -5841,19 +5829,19 @@
         <v>399</v>
       </c>
       <c r="AJ40" t="n">
-        <v>379</v>
+        <v>86</v>
       </c>
       <c r="AK40" t="n">
         <v>0</v>
       </c>
       <c r="AL40" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AM40" t="n">
         <v>0</v>
       </c>
       <c r="AN40" t="n">
-        <v>0</v>
+        <v>375</v>
       </c>
     </row>
     <row r="41">
@@ -5975,19 +5963,19 @@
         <v>350</v>
       </c>
       <c r="AJ41" t="n">
-        <v>335</v>
+        <v>81</v>
       </c>
       <c r="AK41" t="n">
         <v>0</v>
       </c>
       <c r="AL41" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AM41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN41" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="42">
@@ -6109,19 +6097,19 @@
         <v>387</v>
       </c>
       <c r="AJ42" t="n">
-        <v>371</v>
+        <v>127</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AL42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AM42" t="n">
         <v>0</v>
       </c>
       <c r="AN42" t="n">
-        <v>0</v>
+        <v>340</v>
       </c>
     </row>
     <row r="43">
@@ -6243,7 +6231,7 @@
         <v>388</v>
       </c>
       <c r="AJ43" t="n">
-        <v>331</v>
+        <v>42</v>
       </c>
       <c r="AK43" t="n">
         <v>0</v>
@@ -6252,10 +6240,10 @@
         <v>13</v>
       </c>
       <c r="AM43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN43" t="n">
-        <v>1</v>
+        <v>319</v>
       </c>
     </row>
     <row r="44">
@@ -6377,7 +6365,7 @@
         <v>381</v>
       </c>
       <c r="AJ44" t="n">
-        <v>301</v>
+        <v>12</v>
       </c>
       <c r="AK44" t="n">
         <v>0</v>
@@ -6386,206 +6374,206 @@
         <v>9</v>
       </c>
       <c r="AM44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN44" t="n">
-        <v>10</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Fitrianti Tadete</t>
+          <t>Fransiska Paolin Tumbale</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>fitriantitadete68@gmail.com</t>
+          <t>fransiskapaolin@gmail.com</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Derlan Malawere</t>
+          <t>Yulianti Manambe</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>derlanmalawere92@gmail.com</t>
+          <t>anthymanambe8@gmail.com</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>(100) TABUKAN UTARA</t>
+          <t>(092) TAHUNA BARAT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>4450</v>
+        <v>2970</v>
       </c>
       <c r="H45" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="I45" t="n">
-        <v>1.82</v>
+        <v>17.2</v>
       </c>
       <c r="J45" t="n">
-        <v>3030</v>
+        <v>1910</v>
       </c>
       <c r="K45" t="n">
-        <v>345.49</v>
+        <v>491.42</v>
       </c>
       <c r="L45" t="n">
-        <v>85</v>
+        <v>146</v>
       </c>
       <c r="M45" t="n">
-        <v>329</v>
+        <v>236</v>
       </c>
       <c r="N45" t="n">
         <v>1</v>
       </c>
       <c r="O45" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V45" t="n">
-        <v>427</v>
+        <v>477</v>
       </c>
       <c r="W45" t="n">
-        <v>335</v>
+        <v>316</v>
       </c>
       <c r="X45" t="n">
-        <v>85</v>
+        <v>146</v>
       </c>
       <c r="Y45" t="n">
-        <v>329</v>
+        <v>236</v>
       </c>
       <c r="Z45" t="n">
         <v>1</v>
       </c>
       <c r="AA45" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AH45" t="n">
-        <v>427</v>
+        <v>477</v>
       </c>
       <c r="AI45" t="n">
-        <v>335</v>
+        <v>316</v>
       </c>
       <c r="AJ45" t="n">
-        <v>355</v>
+        <v>146</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AL45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AN45" t="n">
-        <v>2</v>
+        <v>236</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Fransiska Paolin Tumbale</t>
+          <t>Frezcilia Dewi Daleda</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>fransiskapaolin@gmail.com</t>
+          <t>frzfrz130293@gmail.com</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Yulianti Manambe</t>
+          <t>Yan Fredrik Wellian Padang</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>anthymanambe8@gmail.com</t>
+          <t>yanfwpadang84@gmail.com</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>(092) TAHUNA BARAT</t>
+          <t>(090) TAHUNA</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>2970</v>
+        <v>1530</v>
       </c>
       <c r="H46" t="n">
-        <v>80</v>
+        <v>260</v>
       </c>
       <c r="I46" t="n">
-        <v>17.2</v>
+        <v>101.69</v>
       </c>
       <c r="J46" t="n">
-        <v>1910</v>
+        <v>440</v>
       </c>
       <c r="K46" t="n">
-        <v>491.42</v>
+        <v>180.61</v>
       </c>
       <c r="L46" t="n">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="M46" t="n">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="N46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="P46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -6597,31 +6585,31 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="U46" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>477</v>
+        <v>433</v>
       </c>
       <c r="W46" t="n">
-        <v>316</v>
+        <v>267</v>
       </c>
       <c r="X46" t="n">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="Y46" t="n">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="Z46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="AB46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6633,263 +6621,263 @@
         <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="AG46" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>477</v>
+        <v>432</v>
       </c>
       <c r="AI46" t="n">
-        <v>316</v>
+        <v>267</v>
       </c>
       <c r="AJ46" t="n">
-        <v>434</v>
+        <v>132</v>
       </c>
       <c r="AK46" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="AL46" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AM46" t="n">
         <v>0</v>
       </c>
       <c r="AN46" t="n">
-        <v>0</v>
+        <v>241</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Frezcilia Dewi Daleda</t>
+          <t>Geovani Marchiano Monok</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>frzfrz130293@gmail.com</t>
+          <t>geovanimonok34@gmail.com</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Yan Fredrik Wellian Padang</t>
+          <t>B. Lenskar Diamanis</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>yanfwpadang84@gmail.com</t>
+          <t>lenskardiamaniz@gmail.com</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>(090) TAHUNA</t>
+          <t>(080) MANGANITU</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>1530</v>
+        <v>2570</v>
       </c>
       <c r="H47" t="n">
-        <v>260</v>
+        <v>40</v>
       </c>
       <c r="I47" t="n">
-        <v>101.69</v>
+        <v>17.52</v>
       </c>
       <c r="J47" t="n">
-        <v>440</v>
+        <v>1790</v>
       </c>
       <c r="K47" t="n">
-        <v>180.61</v>
+        <v>251.34</v>
       </c>
       <c r="L47" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="M47" t="n">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="O47" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="W47" t="n">
-        <v>267</v>
+        <v>299</v>
       </c>
       <c r="X47" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="Y47" t="n">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AA47" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
         <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="AI47" t="n">
-        <v>267</v>
+        <v>299</v>
       </c>
       <c r="AJ47" t="n">
-        <v>375</v>
+        <v>128</v>
       </c>
       <c r="AK47" t="n">
         <v>1</v>
       </c>
       <c r="AL47" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="AM47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AN47" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Geovani Marchiano Monok</t>
+          <t>Geno Pepa Paraso</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>geovanimonok34@gmail.com</t>
+          <t>ghenovhepaparaso@gmail.com</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>B. Lenskar Diamanis</t>
+          <t>Ferdinand Tangkabiringan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>lenskardiamaniz@gmail.com</t>
+          <t>ferdinandtangkabiringan@gmail.com</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>(080) MANGANITU</t>
+          <t>(090) TAHUNA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>2570</v>
+        <v>2280</v>
       </c>
       <c r="H48" t="n">
-        <v>40</v>
+        <v>930</v>
       </c>
       <c r="I48" t="n">
-        <v>17.52</v>
+        <v>88.74000000000001</v>
       </c>
       <c r="J48" t="n">
-        <v>1790</v>
+        <v>590</v>
       </c>
       <c r="K48" t="n">
-        <v>251.34</v>
+        <v>118.55</v>
       </c>
       <c r="L48" t="n">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="M48" t="n">
-        <v>218</v>
+        <v>334</v>
       </c>
       <c r="N48" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="O48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>25</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
+      </c>
+      <c r="V48" t="n">
+        <v>485</v>
+      </c>
+      <c r="W48" t="n">
+        <v>364</v>
+      </c>
+      <c r="X48" t="n">
+        <v>121</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>334</v>
+      </c>
+      <c r="Z48" t="n">
         <v>4</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" t="n">
-        <v>42</v>
-      </c>
-      <c r="U48" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" t="n">
-        <v>428</v>
-      </c>
-      <c r="W48" t="n">
-        <v>299</v>
-      </c>
-      <c r="X48" t="n">
-        <v>128</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>218</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>35</v>
-      </c>
       <c r="AA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6901,19 +6889,19 @@
         <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH48" t="n">
-        <v>428</v>
+        <v>485</v>
       </c>
       <c r="AI48" t="n">
-        <v>299</v>
+        <v>364</v>
       </c>
       <c r="AJ48" t="n">
-        <v>363</v>
+        <v>121</v>
       </c>
       <c r="AK48" t="n">
         <v>0</v>
@@ -6922,471 +6910,471 @@
         <v>4</v>
       </c>
       <c r="AM48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN48" t="n">
-        <v>0</v>
+        <v>334</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Geno Pepa Paraso</t>
+          <t>Grace Dorongpangalo</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ghenovhepaparaso@gmail.com</t>
+          <t>gracedorongpangalo11@gmail.com</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ferdinand Tangkabiringan</t>
+          <t>Fiane Greti Mansauda</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ferdinandtangkabiringan@gmail.com</t>
+          <t>fianemansauda89@gmail.com</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>(090) TAHUNA</t>
+          <t>(070) TABUKAN TENGAH</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>2280</v>
+        <v>3750</v>
       </c>
       <c r="H49" t="n">
-        <v>930</v>
+        <v>160</v>
       </c>
       <c r="I49" t="n">
-        <v>88.74000000000001</v>
+        <v>14.93</v>
       </c>
       <c r="J49" t="n">
-        <v>590</v>
+        <v>3000</v>
       </c>
       <c r="K49" t="n">
-        <v>118.55</v>
+        <v>475.92</v>
       </c>
       <c r="L49" t="n">
-        <v>121</v>
+        <v>178</v>
       </c>
       <c r="M49" t="n">
-        <v>334</v>
+        <v>242</v>
       </c>
       <c r="N49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="U49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V49" t="n">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="W49" t="n">
-        <v>364</v>
+        <v>298</v>
       </c>
       <c r="X49" t="n">
-        <v>121</v>
+        <v>178</v>
       </c>
       <c r="Y49" t="n">
-        <v>334</v>
+        <v>242</v>
       </c>
       <c r="Z49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE49" t="n">
         <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="AG49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH49" t="n">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="AI49" t="n">
-        <v>364</v>
+        <v>298</v>
       </c>
       <c r="AJ49" t="n">
-        <v>411</v>
+        <v>178</v>
       </c>
       <c r="AK49" t="n">
         <v>0</v>
       </c>
       <c r="AL49" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AM49" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AN49" t="n">
-        <v>0</v>
+        <v>242</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Grace Dorongpangalo</t>
+          <t>Grees Pangandaheng</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>gracedorongpangalo11@gmail.com</t>
+          <t>greispangandaheng@gmail.com</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Fiane Greti Mansauda</t>
+          <t>Novdein Arif Bongkitang</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>fianemansauda89@gmail.com</t>
+          <t>novdeinarifbongkitang@gmail.com</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>(070) TABUKAN TENGAH</t>
+          <t>(050) TAMAKO</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>3750</v>
+        <v>3770</v>
       </c>
       <c r="H50" t="n">
-        <v>160</v>
+        <v>110</v>
       </c>
       <c r="I50" t="n">
-        <v>14.93</v>
+        <v>8.950000000000001</v>
       </c>
       <c r="J50" t="n">
-        <v>3000</v>
+        <v>2840</v>
       </c>
       <c r="K50" t="n">
-        <v>475.92</v>
+        <v>302.35</v>
       </c>
       <c r="L50" t="n">
-        <v>178</v>
+        <v>61</v>
       </c>
       <c r="M50" t="n">
-        <v>242</v>
+        <v>398</v>
       </c>
       <c r="N50" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="P50" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="U50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>476</v>
+        <v>539</v>
       </c>
       <c r="W50" t="n">
-        <v>298</v>
+        <v>460</v>
       </c>
       <c r="X50" t="n">
-        <v>178</v>
+        <v>61</v>
       </c>
       <c r="Y50" t="n">
-        <v>242</v>
+        <v>398</v>
       </c>
       <c r="Z50" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AB50" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE50" t="n">
         <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="AG50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH50" t="n">
-        <v>476</v>
+        <v>539</v>
       </c>
       <c r="AI50" t="n">
-        <v>298</v>
+        <v>460</v>
       </c>
       <c r="AJ50" t="n">
-        <v>372</v>
+        <v>61</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AL50" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AM50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AN50" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Grees Pangandaheng</t>
+          <t>Hasrita Hamenda</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>greispangandaheng@gmail.com</t>
+          <t>hamendahasrita@gmail.com</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Novdein Arif Bongkitang</t>
+          <t>Novrilley Richard Mumu</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>novdeinarifbongkitang@gmail.com</t>
+          <t>novrilleymumu11@gmail.com</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>(050) TAMAKO</t>
+          <t>(100) TABUKAN UTARA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>3770</v>
+        <v>4490</v>
       </c>
       <c r="H51" t="n">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="I51" t="n">
-        <v>8.950000000000001</v>
+        <v>20.14</v>
       </c>
       <c r="J51" t="n">
-        <v>2840</v>
+        <v>3690</v>
       </c>
       <c r="K51" t="n">
-        <v>302.35</v>
+        <v>417.55</v>
       </c>
       <c r="L51" t="n">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="M51" t="n">
-        <v>398</v>
+        <v>331</v>
       </c>
       <c r="N51" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O51" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>50</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
+      </c>
+      <c r="V51" t="n">
+        <v>482</v>
+      </c>
+      <c r="W51" t="n">
+        <v>390</v>
+      </c>
+      <c r="X51" t="n">
+        <v>89</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>331</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA51" t="n">
         <v>3</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" t="n">
-        <v>52</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" t="n">
-        <v>539</v>
-      </c>
-      <c r="W51" t="n">
-        <v>460</v>
-      </c>
-      <c r="X51" t="n">
-        <v>61</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>398</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>18</v>
-      </c>
       <c r="AB51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>482</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>390</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>89</v>
+      </c>
+      <c r="AK51" t="n">
         <v>3</v>
       </c>
-      <c r="AC51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>52</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>539</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>460</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>395</v>
-      </c>
-      <c r="AK51" t="n">
-        <v>0</v>
-      </c>
       <c r="AL51" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="AM51" t="n">
         <v>0</v>
       </c>
       <c r="AN51" t="n">
-        <v>0</v>
+        <v>331</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Hasrita Hamenda</t>
+          <t>Wahyudi Hapit</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>hamendahasrita@gmail.com</t>
+          <t>hapitudhy@gmail.com</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Novrilley Richard Mumu</t>
+          <t>Ivonne Lariunaung</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>novrilleymumu11@gmail.com</t>
+          <t>vonnelariunaung77560@gmail.com</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>(100) TABUKAN UTARA</t>
+          <t>(091) TAHUNA TIMUR</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>4490</v>
+        <v>2990</v>
       </c>
       <c r="H52" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="I52" t="n">
-        <v>20.14</v>
+        <v>28.19</v>
       </c>
       <c r="J52" t="n">
-        <v>3690</v>
+        <v>2290</v>
       </c>
       <c r="K52" t="n">
-        <v>417.55</v>
+        <v>300.5</v>
       </c>
       <c r="L52" t="n">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="M52" t="n">
-        <v>331</v>
+        <v>295</v>
       </c>
       <c r="N52" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P52" t="n">
         <v>0</v>
@@ -7395,34 +7383,34 @@
         <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="U52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="W52" t="n">
-        <v>390</v>
+        <v>359</v>
       </c>
       <c r="X52" t="n">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="Y52" t="n">
-        <v>331</v>
+        <v>295</v>
       </c>
       <c r="Z52" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AB52" t="n">
         <v>0</v>
@@ -7431,28 +7419,28 @@
         <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE52" t="n">
         <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="AG52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="n">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="AI52" t="n">
-        <v>390</v>
+        <v>359</v>
       </c>
       <c r="AJ52" t="n">
-        <v>378</v>
+        <v>104</v>
       </c>
       <c r="AK52" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AL52" t="n">
         <v>0</v>
@@ -7461,28 +7449,28 @@
         <v>0</v>
       </c>
       <c r="AN52" t="n">
-        <v>0</v>
+        <v>295</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Wahyudi Hapit</t>
+          <t>Christianto Harilama</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>hapitudhy@gmail.com</t>
+          <t>harilamachris23@gmail.com</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ivonne Lariunaung</t>
+          <t>Jenie Oktavin Rahmawati Monok</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>vonnelariunaung77560@gmail.com</t>
+          <t>jeniemonok7@gmail.com</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -7496,171 +7484,171 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>3060</v>
+        <v>3080</v>
       </c>
       <c r="H53" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="I53" t="n">
-        <v>30.84</v>
+        <v>71.77</v>
       </c>
       <c r="J53" t="n">
-        <v>2260</v>
+        <v>2490</v>
       </c>
       <c r="K53" t="n">
-        <v>358.47</v>
+        <v>636.87</v>
       </c>
       <c r="L53" t="n">
-        <v>104</v>
+        <v>150</v>
       </c>
       <c r="M53" t="n">
-        <v>341</v>
+        <v>219</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O53" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V53" t="n">
-        <v>493</v>
+        <v>452</v>
       </c>
       <c r="W53" t="n">
-        <v>382</v>
+        <v>279</v>
       </c>
       <c r="X53" t="n">
-        <v>104</v>
+        <v>150</v>
       </c>
       <c r="Y53" t="n">
-        <v>341</v>
+        <v>219</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA53" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
         <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH53" t="n">
-        <v>493</v>
+        <v>452</v>
       </c>
       <c r="AI53" t="n">
-        <v>382</v>
+        <v>279</v>
       </c>
       <c r="AJ53" t="n">
-        <v>429</v>
+        <v>150</v>
       </c>
       <c r="AK53" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="AL53" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="AM53" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="AN53" t="n">
-        <v>1</v>
+        <v>219</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Christianto Harilama</t>
+          <t>Sintike Susanti Meling Horman</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>harilamachris23@gmail.com</t>
+          <t>hshyntike@gmail.com</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jenie Oktavin Rahmawati Monok</t>
+          <t>Ningsi Karendehi</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>jeniemonok7@gmail.com</t>
+          <t>ningsikarendehi968@gmail.com</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>(091) TAHUNA TIMUR</t>
+          <t>(061) TABUKAN SELATAN TENGAH &amp; (062) TABUKAN SELATAN TENGGARA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Erwin &amp; Lalu</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>2250</v>
+        <v>3950</v>
       </c>
       <c r="H54" t="n">
         <v>90</v>
       </c>
       <c r="I54" t="n">
-        <v>65.06</v>
+        <v>20.57</v>
       </c>
       <c r="J54" t="n">
-        <v>2040</v>
+        <v>2720</v>
       </c>
       <c r="K54" t="n">
-        <v>608.73</v>
+        <v>496.06</v>
       </c>
       <c r="L54" t="n">
-        <v>201</v>
+        <v>83</v>
       </c>
       <c r="M54" t="n">
-        <v>166</v>
+        <v>235</v>
       </c>
       <c r="N54" t="n">
         <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
@@ -7669,34 +7657,34 @@
         <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>12</v>
+        <v>78</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V54" t="n">
-        <v>433</v>
+        <v>400</v>
       </c>
       <c r="W54" t="n">
-        <v>201</v>
+        <v>317</v>
       </c>
       <c r="X54" t="n">
-        <v>201</v>
+        <v>83</v>
       </c>
       <c r="Y54" t="n">
-        <v>166</v>
+        <v>235</v>
       </c>
       <c r="Z54" t="n">
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD54" t="n">
         <v>0</v>
@@ -7705,96 +7693,96 @@
         <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>12</v>
+        <v>78</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH54" t="n">
-        <v>433</v>
+        <v>400</v>
       </c>
       <c r="AI54" t="n">
-        <v>201</v>
+        <v>317</v>
       </c>
       <c r="AJ54" t="n">
-        <v>396</v>
+        <v>83</v>
       </c>
       <c r="AK54" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AL54" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AM54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN54" t="n">
-        <v>2</v>
+        <v>235</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sintike Susanti Meling Horman</t>
+          <t>Siti Nurhayati Igirisa</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>hshyntike@gmail.com</t>
+          <t>igirisatia5@gmail.com</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ningsi Karendehi</t>
+          <t>Yan Fredrik Wellian Padang</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ningsikarendehi968@gmail.com</t>
+          <t>yanfwpadang84@gmail.com</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>(061) TABUKAN SELATAN TENGAH &amp; (062) TABUKAN SELATAN TENGGARA</t>
+          <t>(090) TAHUNA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Erwin &amp; Lalu</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>3950</v>
+        <v>1940</v>
       </c>
       <c r="H55" t="n">
-        <v>90</v>
+        <v>450</v>
       </c>
       <c r="I55" t="n">
-        <v>20.57</v>
+        <v>98.07000000000001</v>
       </c>
       <c r="J55" t="n">
-        <v>2720</v>
+        <v>970</v>
       </c>
       <c r="K55" t="n">
-        <v>496.06</v>
+        <v>197.18</v>
       </c>
       <c r="L55" t="n">
-        <v>83</v>
+        <v>160</v>
       </c>
       <c r="M55" t="n">
-        <v>235</v>
+        <v>403</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="P55" t="n">
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
@@ -7803,34 +7791,34 @@
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="U55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V55" t="n">
-        <v>400</v>
+        <v>636</v>
       </c>
       <c r="W55" t="n">
-        <v>317</v>
+        <v>431</v>
       </c>
       <c r="X55" t="n">
-        <v>83</v>
+        <v>160</v>
       </c>
       <c r="Y55" t="n">
-        <v>235</v>
+        <v>403</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AB55" t="n">
         <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
         <v>0</v>
@@ -7839,93 +7827,93 @@
         <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="AG55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AH55" t="n">
-        <v>400</v>
+        <v>636</v>
       </c>
       <c r="AI55" t="n">
-        <v>317</v>
+        <v>431</v>
       </c>
       <c r="AJ55" t="n">
-        <v>279</v>
+        <v>160</v>
       </c>
       <c r="AK55" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AL55" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="AM55" t="n">
         <v>0</v>
       </c>
       <c r="AN55" t="n">
-        <v>0</v>
+        <v>403</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Siti Nurhayati Igirisa</t>
+          <t>Suryaningsi Dorthea Lalompoh</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>igirisatia5@gmail.com</t>
+          <t>indrydorthea@gmail.com</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Yan Fredrik Wellian Padang</t>
+          <t>Jekir Venkil Dompas</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>yanfwpadang84@gmail.com</t>
+          <t>jekirvenkildompas@gmail.com</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>(090) TAHUNA</t>
+          <t>(070) TABUKAN TENGAH</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>1940</v>
+        <v>4770</v>
       </c>
       <c r="H56" t="n">
-        <v>450</v>
+        <v>140</v>
       </c>
       <c r="I56" t="n">
-        <v>98.07000000000001</v>
+        <v>15.48</v>
       </c>
       <c r="J56" t="n">
-        <v>970</v>
+        <v>3510</v>
       </c>
       <c r="K56" t="n">
-        <v>197.18</v>
+        <v>444.19</v>
       </c>
       <c r="L56" t="n">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="M56" t="n">
-        <v>403</v>
+        <v>215</v>
       </c>
       <c r="N56" t="n">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="O56" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -7937,31 +7925,31 @@
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="U56" t="n">
         <v>1</v>
       </c>
       <c r="V56" t="n">
-        <v>636</v>
+        <v>493</v>
       </c>
       <c r="W56" t="n">
-        <v>431</v>
+        <v>328</v>
       </c>
       <c r="X56" t="n">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="Y56" t="n">
-        <v>403</v>
+        <v>215</v>
       </c>
       <c r="Z56" t="n">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="AA56" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7973,93 +7961,93 @@
         <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="AG56" t="n">
         <v>1</v>
       </c>
       <c r="AH56" t="n">
-        <v>636</v>
+        <v>493</v>
       </c>
       <c r="AI56" t="n">
-        <v>431</v>
+        <v>328</v>
       </c>
       <c r="AJ56" t="n">
-        <v>420</v>
+        <v>148</v>
       </c>
       <c r="AK56" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AL56" t="n">
-        <v>8</v>
+        <v>73</v>
       </c>
       <c r="AM56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN56" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Suryaningsi Dorthea Lalompoh</t>
+          <t>Asiantina Maniku</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>indrydorthea@gmail.com</t>
+          <t>iyanmaniku1@gmail.com</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jekir Venkil Dompas</t>
+          <t>Derlan Malawere</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>jekirvenkildompas@gmail.com</t>
+          <t>derlanmalawere92@gmail.com</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>(070) TABUKAN TENGAH</t>
+          <t>(100) TABUKAN UTARA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>4770</v>
+        <v>4450</v>
       </c>
       <c r="H57" t="n">
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="I57" t="n">
-        <v>15.48</v>
+        <v>1.82</v>
       </c>
       <c r="J57" t="n">
-        <v>3510</v>
+        <v>3030</v>
       </c>
       <c r="K57" t="n">
-        <v>444.19</v>
+        <v>345.49</v>
       </c>
       <c r="L57" t="n">
-        <v>148</v>
+        <v>85</v>
       </c>
       <c r="M57" t="n">
-        <v>215</v>
+        <v>329</v>
       </c>
       <c r="N57" t="n">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="O57" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="P57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -8071,31 +8059,31 @@
         <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="U57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V57" t="n">
-        <v>493</v>
+        <v>427</v>
       </c>
       <c r="W57" t="n">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="X57" t="n">
-        <v>148</v>
+        <v>85</v>
       </c>
       <c r="Y57" t="n">
-        <v>215</v>
+        <v>329</v>
       </c>
       <c r="Z57" t="n">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="AA57" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="AB57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -8107,31 +8095,31 @@
         <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="AG57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH57" t="n">
-        <v>493</v>
+        <v>427</v>
       </c>
       <c r="AI57" t="n">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="AJ57" t="n">
-        <v>336</v>
+        <v>85</v>
       </c>
       <c r="AK57" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AL57" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AM57" t="n">
         <v>0</v>
       </c>
       <c r="AN57" t="n">
-        <v>0</v>
+        <v>329</v>
       </c>
     </row>
     <row r="58">
@@ -8253,19 +8241,19 @@
         <v>267</v>
       </c>
       <c r="AJ58" t="n">
-        <v>363</v>
+        <v>194</v>
       </c>
       <c r="AK58" t="n">
         <v>0</v>
       </c>
       <c r="AL58" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AM58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN58" t="n">
-        <v>0</v>
+        <v>207</v>
       </c>
     </row>
     <row r="59">
@@ -8387,19 +8375,19 @@
         <v>364</v>
       </c>
       <c r="AJ59" t="n">
-        <v>383</v>
+        <v>108</v>
       </c>
       <c r="AK59" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AL59" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AM59" t="n">
         <v>0</v>
       </c>
       <c r="AN59" t="n">
-        <v>1</v>
+        <v>252</v>
       </c>
     </row>
     <row r="60">
@@ -8521,19 +8509,19 @@
         <v>289</v>
       </c>
       <c r="AJ60" t="n">
-        <v>377</v>
+        <v>160</v>
       </c>
       <c r="AK60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL60" t="n">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="AM60" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AN60" t="n">
-        <v>0</v>
+        <v>142</v>
       </c>
     </row>
     <row r="61">
@@ -8655,19 +8643,19 @@
         <v>238</v>
       </c>
       <c r="AJ61" t="n">
-        <v>314</v>
+        <v>126</v>
       </c>
       <c r="AK61" t="n">
         <v>0</v>
       </c>
       <c r="AL61" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AM61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN61" t="n">
-        <v>0</v>
+        <v>181</v>
       </c>
     </row>
     <row r="62">
@@ -8789,19 +8777,19 @@
         <v>440</v>
       </c>
       <c r="AJ62" t="n">
-        <v>365</v>
+        <v>79</v>
       </c>
       <c r="AK62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL62" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="AM62" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AN62" t="n">
-        <v>6</v>
+        <v>345</v>
       </c>
     </row>
     <row r="63">
@@ -8923,19 +8911,19 @@
         <v>373</v>
       </c>
       <c r="AJ63" t="n">
-        <v>324</v>
+        <v>99</v>
       </c>
       <c r="AK63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL63" t="n">
         <v>0</v>
       </c>
       <c r="AM63" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AN63" t="n">
-        <v>0</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64">
@@ -9057,19 +9045,19 @@
         <v>394</v>
       </c>
       <c r="AJ64" t="n">
-        <v>440</v>
+        <v>157</v>
       </c>
       <c r="AK64" t="n">
         <v>0</v>
       </c>
       <c r="AL64" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AM64" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AN64" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
     </row>
     <row r="65">
@@ -9191,19 +9179,19 @@
         <v>357</v>
       </c>
       <c r="AJ65" t="n">
-        <v>417</v>
+        <v>105</v>
       </c>
       <c r="AK65" t="n">
         <v>0</v>
       </c>
       <c r="AL65" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AM65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN65" t="n">
-        <v>0</v>
+        <v>291</v>
       </c>
     </row>
     <row r="66">
@@ -9325,19 +9313,19 @@
         <v>397</v>
       </c>
       <c r="AJ66" t="n">
-        <v>384</v>
+        <v>78</v>
       </c>
       <c r="AK66" t="n">
         <v>0</v>
       </c>
       <c r="AL66" t="n">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="AM66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN66" t="n">
-        <v>2</v>
+        <v>316</v>
       </c>
     </row>
     <row r="67">
@@ -9459,19 +9447,19 @@
         <v>255</v>
       </c>
       <c r="AJ67" t="n">
-        <v>297</v>
+        <v>100</v>
       </c>
       <c r="AK67" t="n">
         <v>0</v>
       </c>
       <c r="AL67" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="AM67" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AN67" t="n">
-        <v>1</v>
+        <v>185</v>
       </c>
     </row>
     <row r="68">
@@ -9593,19 +9581,19 @@
         <v>504</v>
       </c>
       <c r="AJ68" t="n">
-        <v>395</v>
+        <v>21</v>
       </c>
       <c r="AK68" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AL68" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="AM68" t="n">
         <v>1</v>
       </c>
       <c r="AN68" t="n">
-        <v>8</v>
+        <v>448</v>
       </c>
     </row>
     <row r="69">
@@ -9727,19 +9715,19 @@
         <v>300</v>
       </c>
       <c r="AJ69" t="n">
-        <v>317</v>
+        <v>101</v>
       </c>
       <c r="AK69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AL69" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="AM69" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AN69" t="n">
-        <v>0</v>
+        <v>227</v>
       </c>
     </row>
     <row r="70">
@@ -9861,19 +9849,19 @@
         <v>224</v>
       </c>
       <c r="AJ70" t="n">
-        <v>306</v>
+        <v>131</v>
       </c>
       <c r="AK70" t="n">
         <v>0</v>
       </c>
       <c r="AL70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM70" t="n">
         <v>0</v>
       </c>
       <c r="AN70" t="n">
-        <v>0</v>
+        <v>195</v>
       </c>
     </row>
     <row r="71">
@@ -9995,19 +9983,19 @@
         <v>441</v>
       </c>
       <c r="AJ71" t="n">
-        <v>366</v>
+        <v>80</v>
       </c>
       <c r="AK71" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AL71" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AM71" t="n">
         <v>0</v>
       </c>
       <c r="AN71" t="n">
-        <v>0</v>
+        <v>391</v>
       </c>
     </row>
     <row r="72">
@@ -10129,19 +10117,19 @@
         <v>578</v>
       </c>
       <c r="AJ72" t="n">
-        <v>353</v>
+        <v>3</v>
       </c>
       <c r="AK72" t="n">
         <v>0</v>
       </c>
       <c r="AL72" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AM72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN72" t="n">
-        <v>0</v>
+        <v>492</v>
       </c>
     </row>
     <row r="73">
@@ -10263,19 +10251,19 @@
         <v>331</v>
       </c>
       <c r="AJ73" t="n">
-        <v>362</v>
+        <v>105</v>
       </c>
       <c r="AK73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL73" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AM73" t="n">
         <v>0</v>
       </c>
       <c r="AN73" t="n">
-        <v>0</v>
+        <v>289</v>
       </c>
     </row>
     <row r="74">
@@ -10397,10 +10385,10 @@
         <v>472</v>
       </c>
       <c r="AJ74" t="n">
-        <v>398</v>
+        <v>19</v>
       </c>
       <c r="AK74" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="AL74" t="n">
         <v>0</v>
@@ -10409,7 +10397,7 @@
         <v>0</v>
       </c>
       <c r="AN74" t="n">
-        <v>0</v>
+        <v>386</v>
       </c>
     </row>
     <row r="75">
@@ -10531,19 +10519,19 @@
         <v>283</v>
       </c>
       <c r="AJ75" t="n">
-        <v>359</v>
+        <v>138</v>
       </c>
       <c r="AK75" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AL75" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AM75" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AN75" t="n">
-        <v>0</v>
+        <v>233</v>
       </c>
     </row>
     <row r="76">
@@ -10665,19 +10653,19 @@
         <v>251</v>
       </c>
       <c r="AJ76" t="n">
-        <v>357</v>
+        <v>175</v>
       </c>
       <c r="AK76" t="n">
         <v>0</v>
       </c>
       <c r="AL76" t="n">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="AM76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN76" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
     </row>
     <row r="77">
@@ -10799,19 +10787,19 @@
         <v>430</v>
       </c>
       <c r="AJ77" t="n">
-        <v>386</v>
+        <v>87</v>
       </c>
       <c r="AK77" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="AL77" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="AM77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN77" t="n">
-        <v>7</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78">
@@ -10933,19 +10921,19 @@
         <v>306</v>
       </c>
       <c r="AJ78" t="n">
-        <v>350</v>
+        <v>114</v>
       </c>
       <c r="AK78" t="n">
         <v>0</v>
       </c>
       <c r="AL78" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="AM78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN78" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
     </row>
     <row r="79">
@@ -11067,7 +11055,7 @@
         <v>394</v>
       </c>
       <c r="AJ79" t="n">
-        <v>319</v>
+        <v>21</v>
       </c>
       <c r="AK79" t="n">
         <v>0</v>
@@ -11076,144 +11064,144 @@
         <v>6</v>
       </c>
       <c r="AM79" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AN79" t="n">
-        <v>7</v>
+        <v>313</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Mery Grace Anabelia Kantohe</t>
+          <t>Aldo Jhon Mesak Bangonang</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>merykantohe979@gmail.com</t>
+          <t>mesakbangonang99@gmail.com</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Hastuti Manabung</t>
+          <t>Ivonne Lariunaung</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>hmanabung01@gmail.com</t>
+          <t>vonnelariunaung77560@gmail.com</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>(110) KENDAHE</t>
+          <t>(091) TAHUNA TIMUR</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>2270</v>
+        <v>1820</v>
       </c>
       <c r="H80" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="I80" t="n">
-        <v>7.34</v>
+        <v>20.13</v>
       </c>
       <c r="J80" t="n">
-        <v>1930</v>
+        <v>1280</v>
       </c>
       <c r="K80" t="n">
-        <v>339.22</v>
+        <v>367.04</v>
       </c>
       <c r="L80" t="n">
-        <v>95</v>
+        <v>211</v>
       </c>
       <c r="M80" t="n">
-        <v>149</v>
+        <v>108</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O80" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="P80" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
       </c>
       <c r="T80" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="U80" t="n">
         <v>0</v>
       </c>
       <c r="V80" t="n">
-        <v>289</v>
+        <v>390</v>
       </c>
       <c r="W80" t="n">
-        <v>194</v>
+        <v>161</v>
       </c>
       <c r="X80" t="n">
-        <v>95</v>
+        <v>213</v>
       </c>
       <c r="Y80" t="n">
-        <v>149</v>
+        <v>108</v>
       </c>
       <c r="Z80" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AB80" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
       </c>
       <c r="AD80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE80" t="n">
         <v>0</v>
       </c>
       <c r="AF80" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
       </c>
       <c r="AH80" t="n">
-        <v>289</v>
+        <v>390</v>
       </c>
       <c r="AI80" t="n">
-        <v>194</v>
+        <v>159</v>
       </c>
       <c r="AJ80" t="n">
-        <v>263</v>
+        <v>211</v>
       </c>
       <c r="AK80" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="AL80" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AM80" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AN80" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
     </row>
     <row r="81">
@@ -11335,19 +11323,19 @@
         <v>292</v>
       </c>
       <c r="AJ81" t="n">
-        <v>313</v>
+        <v>60</v>
       </c>
       <c r="AK81" t="n">
         <v>0</v>
       </c>
       <c r="AL81" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AM81" t="n">
         <v>0</v>
       </c>
       <c r="AN81" t="n">
-        <v>0</v>
+        <v>262</v>
       </c>
     </row>
     <row r="82">
@@ -11469,19 +11457,19 @@
         <v>330</v>
       </c>
       <c r="AJ82" t="n">
-        <v>385</v>
+        <v>113</v>
       </c>
       <c r="AK82" t="n">
         <v>0</v>
       </c>
       <c r="AL82" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AM82" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AN82" t="n">
-        <v>0</v>
+        <v>282</v>
       </c>
     </row>
     <row r="83">
@@ -11603,19 +11591,19 @@
         <v>299</v>
       </c>
       <c r="AJ83" t="n">
-        <v>340</v>
+        <v>159</v>
       </c>
       <c r="AK83" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AL83" t="n">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="AM83" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AN83" t="n">
-        <v>0</v>
+        <v>214</v>
       </c>
     </row>
     <row r="84">
@@ -11737,19 +11725,19 @@
         <v>316</v>
       </c>
       <c r="AJ84" t="n">
-        <v>378</v>
+        <v>111</v>
       </c>
       <c r="AK84" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="AL84" t="n">
         <v>0</v>
       </c>
       <c r="AM84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN84" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="85">
@@ -11871,19 +11859,19 @@
         <v>299</v>
       </c>
       <c r="AJ85" t="n">
-        <v>367</v>
+        <v>126</v>
       </c>
       <c r="AK85" t="n">
         <v>0</v>
       </c>
       <c r="AL85" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AM85" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AN85" t="n">
-        <v>0</v>
+        <v>236</v>
       </c>
     </row>
     <row r="86">
@@ -12005,19 +11993,19 @@
         <v>327</v>
       </c>
       <c r="AJ86" t="n">
-        <v>367</v>
+        <v>163</v>
       </c>
       <c r="AK86" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="AL86" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AM86" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AN86" t="n">
-        <v>0</v>
+        <v>264</v>
       </c>
     </row>
     <row r="87">
@@ -12139,19 +12127,19 @@
         <v>278</v>
       </c>
       <c r="AJ87" t="n">
-        <v>360</v>
+        <v>146</v>
       </c>
       <c r="AK87" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="AL87" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="AM87" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AN87" t="n">
-        <v>0</v>
+        <v>171</v>
       </c>
     </row>
     <row r="88">
@@ -12273,19 +12261,19 @@
         <v>362</v>
       </c>
       <c r="AJ88" t="n">
-        <v>356</v>
+        <v>70</v>
       </c>
       <c r="AK88" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="AL88" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AM88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AN88" t="n">
-        <v>0</v>
+        <v>329</v>
       </c>
     </row>
     <row r="89">
@@ -12407,19 +12395,19 @@
         <v>333</v>
       </c>
       <c r="AJ89" t="n">
-        <v>405</v>
+        <v>167</v>
       </c>
       <c r="AK89" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="AL89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM89" t="n">
         <v>2</v>
       </c>
-      <c r="AM89" t="n">
-        <v>0</v>
-      </c>
       <c r="AN89" t="n">
-        <v>0</v>
+        <v>264</v>
       </c>
     </row>
     <row r="90">
@@ -12541,19 +12529,19 @@
         <v>239</v>
       </c>
       <c r="AJ90" t="n">
-        <v>301</v>
+        <v>51</v>
       </c>
       <c r="AK90" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AL90" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="AM90" t="n">
         <v>0</v>
       </c>
       <c r="AN90" t="n">
-        <v>0</v>
+        <v>207</v>
       </c>
     </row>
     <row r="91">
@@ -12675,19 +12663,19 @@
         <v>316</v>
       </c>
       <c r="AJ91" t="n">
-        <v>399</v>
+        <v>127</v>
       </c>
       <c r="AK91" t="n">
         <v>0</v>
       </c>
       <c r="AL91" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="AM91" t="n">
         <v>0</v>
       </c>
       <c r="AN91" t="n">
-        <v>0</v>
+        <v>293</v>
       </c>
     </row>
     <row r="92">
@@ -12809,19 +12797,19 @@
         <v>360</v>
       </c>
       <c r="AJ92" t="n">
-        <v>364</v>
+        <v>108</v>
       </c>
       <c r="AK92" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AL92" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AM92" t="n">
         <v>0</v>
       </c>
       <c r="AN92" t="n">
-        <v>0</v>
+        <v>324</v>
       </c>
     </row>
     <row r="93">
@@ -12943,19 +12931,19 @@
         <v>381</v>
       </c>
       <c r="AJ93" t="n">
-        <v>335</v>
+        <v>42</v>
       </c>
       <c r="AK93" t="n">
         <v>0</v>
       </c>
       <c r="AL93" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AM93" t="n">
         <v>0</v>
       </c>
       <c r="AN93" t="n">
-        <v>0</v>
+        <v>347</v>
       </c>
     </row>
     <row r="94">
@@ -13077,10 +13065,10 @@
         <v>278</v>
       </c>
       <c r="AJ94" t="n">
-        <v>373</v>
+        <v>164</v>
       </c>
       <c r="AK94" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="AL94" t="n">
         <v>4</v>
@@ -13089,7 +13077,7 @@
         <v>0</v>
       </c>
       <c r="AN94" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
     </row>
     <row r="95">
@@ -13211,19 +13199,19 @@
         <v>382</v>
       </c>
       <c r="AJ95" t="n">
-        <v>356</v>
+        <v>47</v>
       </c>
       <c r="AK95" t="n">
         <v>0</v>
       </c>
       <c r="AL95" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="AM95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN95" t="n">
-        <v>3</v>
+        <v>325</v>
       </c>
     </row>
     <row r="96">
@@ -13345,19 +13333,19 @@
         <v>366</v>
       </c>
       <c r="AJ96" t="n">
-        <v>282</v>
+        <v>30</v>
       </c>
       <c r="AK96" t="n">
         <v>0</v>
       </c>
       <c r="AL96" t="n">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="AM96" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AN96" t="n">
-        <v>1</v>
+        <v>247</v>
       </c>
     </row>
     <row r="97">
@@ -13479,19 +13467,19 @@
         <v>360</v>
       </c>
       <c r="AJ97" t="n">
-        <v>378</v>
+        <v>21</v>
       </c>
       <c r="AK97" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="AL97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM97" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AN97" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
     </row>
     <row r="98">
@@ -13613,19 +13601,19 @@
         <v>248</v>
       </c>
       <c r="AJ98" t="n">
-        <v>367</v>
+        <v>152</v>
       </c>
       <c r="AK98" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL98" t="n">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="AM98" t="n">
         <v>0</v>
       </c>
       <c r="AN98" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
     </row>
     <row r="99">
@@ -13747,19 +13735,19 @@
         <v>347</v>
       </c>
       <c r="AJ99" t="n">
-        <v>321</v>
+        <v>87</v>
       </c>
       <c r="AK99" t="n">
         <v>0</v>
       </c>
       <c r="AL99" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AM99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN99" t="n">
-        <v>0</v>
+        <v>251</v>
       </c>
     </row>
     <row r="100">
@@ -13881,19 +13869,19 @@
         <v>277</v>
       </c>
       <c r="AJ100" t="n">
-        <v>343</v>
+        <v>161</v>
       </c>
       <c r="AK100" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AL100" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="AM100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN100" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
     </row>
     <row r="101">
@@ -14015,19 +14003,19 @@
         <v>399</v>
       </c>
       <c r="AJ101" t="n">
-        <v>455</v>
+        <v>134</v>
       </c>
       <c r="AK101" t="n">
         <v>0</v>
       </c>
       <c r="AL101" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AM101" t="n">
         <v>0</v>
       </c>
       <c r="AN101" t="n">
-        <v>0</v>
+        <v>281</v>
       </c>
     </row>
     <row r="102">
@@ -14058,7 +14046,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -14149,19 +14137,19 @@
         <v>318</v>
       </c>
       <c r="AJ102" t="n">
-        <v>472</v>
+        <v>192</v>
       </c>
       <c r="AK102" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AL102" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM102" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AN102" t="n">
-        <v>0</v>
+        <v>248</v>
       </c>
     </row>
     <row r="103">
@@ -14283,19 +14271,19 @@
         <v>427</v>
       </c>
       <c r="AJ103" t="n">
-        <v>316</v>
+        <v>0</v>
       </c>
       <c r="AK103" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AL103" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="AM103" t="n">
         <v>0</v>
       </c>
       <c r="AN103" t="n">
-        <v>0</v>
+        <v>364</v>
       </c>
     </row>
     <row r="104">
@@ -14326,7 +14314,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -14417,19 +14405,19 @@
         <v>296</v>
       </c>
       <c r="AJ104" t="n">
-        <v>422</v>
+        <v>139</v>
       </c>
       <c r="AK104" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="AL104" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AM104" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AN104" t="n">
-        <v>0</v>
+        <v>233</v>
       </c>
     </row>
     <row r="105">
@@ -14464,25 +14452,25 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>3820</v>
+        <v>3890</v>
       </c>
       <c r="H105" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="I105" t="n">
-        <v>51.16999999999999</v>
+        <v>53.81999999999999</v>
       </c>
       <c r="J105" t="n">
-        <v>2670</v>
+        <v>2640</v>
       </c>
       <c r="K105" t="n">
-        <v>399.42</v>
+        <v>457.39</v>
       </c>
       <c r="L105" t="n">
         <v>87</v>
       </c>
       <c r="M105" t="n">
-        <v>304</v>
+        <v>350</v>
       </c>
       <c r="N105" t="n">
         <v>16</v>
@@ -14503,22 +14491,22 @@
         <v>0</v>
       </c>
       <c r="T105" t="n">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="U105" t="n">
         <v>0</v>
       </c>
       <c r="V105" t="n">
-        <v>503</v>
+        <v>526</v>
       </c>
       <c r="W105" t="n">
-        <v>408</v>
+        <v>431</v>
       </c>
       <c r="X105" t="n">
         <v>87</v>
       </c>
       <c r="Y105" t="n">
-        <v>304</v>
+        <v>350</v>
       </c>
       <c r="Z105" t="n">
         <v>16</v>
@@ -14539,31 +14527,31 @@
         <v>0</v>
       </c>
       <c r="AF105" t="n">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="AG105" t="n">
         <v>0</v>
       </c>
       <c r="AH105" t="n">
-        <v>503</v>
+        <v>526</v>
       </c>
       <c r="AI105" t="n">
-        <v>408</v>
+        <v>431</v>
       </c>
       <c r="AJ105" t="n">
-        <v>391</v>
+        <v>87</v>
       </c>
       <c r="AK105" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AL105" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AM105" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AN105" t="n">
-        <v>5</v>
+        <v>350</v>
       </c>
     </row>
     <row r="106">
@@ -14685,19 +14673,19 @@
         <v>395</v>
       </c>
       <c r="AJ106" t="n">
-        <v>366</v>
+        <v>113</v>
       </c>
       <c r="AK106" t="n">
         <v>1</v>
       </c>
       <c r="AL106" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="AM106" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AN106" t="n">
-        <v>11</v>
+        <v>299</v>
       </c>
     </row>
     <row r="107">
@@ -14819,19 +14807,19 @@
         <v>307</v>
       </c>
       <c r="AJ107" t="n">
-        <v>322</v>
+        <v>72</v>
       </c>
       <c r="AK107" t="n">
         <v>0</v>
       </c>
       <c r="AL107" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AM107" t="n">
         <v>0</v>
       </c>
       <c r="AN107" t="n">
-        <v>0</v>
+        <v>231</v>
       </c>
     </row>
     <row r="108">
@@ -14953,19 +14941,19 @@
         <v>368</v>
       </c>
       <c r="AJ108" t="n">
-        <v>324</v>
+        <v>32</v>
       </c>
       <c r="AK108" t="n">
         <v>0</v>
       </c>
       <c r="AL108" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AM108" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AN108" t="n">
-        <v>5</v>
+        <v>304</v>
       </c>
     </row>
     <row r="109">
@@ -15087,10 +15075,10 @@
         <v>313</v>
       </c>
       <c r="AJ109" t="n">
-        <v>407</v>
+        <v>193</v>
       </c>
       <c r="AK109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL109" t="n">
         <v>2</v>
@@ -15099,7 +15087,7 @@
         <v>0</v>
       </c>
       <c r="AN109" t="n">
-        <v>0</v>
+        <v>269</v>
       </c>
     </row>
     <row r="110">
@@ -15221,10 +15209,10 @@
         <v>404</v>
       </c>
       <c r="AJ110" t="n">
-        <v>507</v>
+        <v>213</v>
       </c>
       <c r="AK110" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AL110" t="n">
         <v>0</v>
@@ -15233,7 +15221,7 @@
         <v>3</v>
       </c>
       <c r="AN110" t="n">
-        <v>2</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111">
@@ -15355,19 +15343,19 @@
         <v>307</v>
       </c>
       <c r="AJ111" t="n">
-        <v>294</v>
+        <v>109</v>
       </c>
       <c r="AK111" t="n">
         <v>0</v>
       </c>
       <c r="AL111" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AM111" t="n">
         <v>0</v>
       </c>
       <c r="AN111" t="n">
-        <v>0</v>
+        <v>255</v>
       </c>
     </row>
     <row r="112">
@@ -15489,19 +15477,19 @@
         <v>262</v>
       </c>
       <c r="AJ112" t="n">
-        <v>403</v>
+        <v>178</v>
       </c>
       <c r="AK112" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN112" t="n">
-        <v>0</v>
+        <v>243</v>
       </c>
     </row>
     <row r="113">
@@ -15623,19 +15611,19 @@
         <v>442</v>
       </c>
       <c r="AJ113" t="n">
-        <v>362</v>
+        <v>87</v>
       </c>
       <c r="AK113" t="n">
         <v>0</v>
       </c>
       <c r="AL113" t="n">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="AM113" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AN113" t="n">
-        <v>2</v>
+        <v>286</v>
       </c>
     </row>
     <row r="114">
@@ -15757,19 +15745,19 @@
         <v>561</v>
       </c>
       <c r="AJ114" t="n">
-        <v>382</v>
+        <v>0</v>
       </c>
       <c r="AK114" t="n">
         <v>0</v>
       </c>
       <c r="AL114" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AM114" t="n">
         <v>0</v>
       </c>
       <c r="AN114" t="n">
-        <v>0</v>
+        <v>445</v>
       </c>
     </row>
     <row r="115">
@@ -15891,19 +15879,19 @@
         <v>271</v>
       </c>
       <c r="AJ115" t="n">
-        <v>344</v>
+        <v>162</v>
       </c>
       <c r="AK115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL115" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM115" t="n">
         <v>0</v>
       </c>
       <c r="AN115" t="n">
-        <v>0</v>
+        <v>249</v>
       </c>
     </row>
     <row r="116">
@@ -16025,87 +16013,87 @@
         <v>292</v>
       </c>
       <c r="AJ116" t="n">
-        <v>333</v>
+        <v>102</v>
       </c>
       <c r="AK116" t="n">
         <v>0</v>
       </c>
       <c r="AL116" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="AM116" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AN116" t="n">
-        <v>0</v>
+        <v>224</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Stevanus Francois Mangeghong</t>
+          <t>Srirahayu Durumias</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>stivfrancois@gmail.com</t>
+          <t>srirahayudurumias@gmail.com</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Fresly Jeica Manangkoda</t>
+          <t>Hastuti Manabung</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>fmanangkoda12@gmail.com</t>
+          <t>hmanabung01@gmail.com</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>(050) TAMAKO</t>
+          <t>(110) KENDAHE</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>3870</v>
+        <v>2270</v>
       </c>
       <c r="H117" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="I117" t="n">
-        <v>16.48</v>
+        <v>7.34</v>
       </c>
       <c r="J117" t="n">
-        <v>2840</v>
+        <v>1930</v>
       </c>
       <c r="K117" t="n">
-        <v>485.67</v>
+        <v>339.22</v>
       </c>
       <c r="L117" t="n">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="M117" t="n">
-        <v>320</v>
+        <v>149</v>
       </c>
       <c r="N117" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
       </c>
       <c r="P117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q117" t="n">
         <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -16117,31 +16105,31 @@
         <v>0</v>
       </c>
       <c r="V117" t="n">
-        <v>435</v>
+        <v>289</v>
       </c>
       <c r="W117" t="n">
-        <v>371</v>
+        <v>194</v>
       </c>
       <c r="X117" t="n">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="Y117" t="n">
-        <v>320</v>
+        <v>149</v>
       </c>
       <c r="Z117" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA117" t="n">
         <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
       </c>
       <c r="AD117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE117" t="n">
         <v>0</v>
@@ -16153,81 +16141,81 @@
         <v>0</v>
       </c>
       <c r="AH117" t="n">
-        <v>435</v>
+        <v>289</v>
       </c>
       <c r="AI117" t="n">
-        <v>371</v>
+        <v>194</v>
       </c>
       <c r="AJ117" t="n">
-        <v>364</v>
+        <v>95</v>
       </c>
       <c r="AK117" t="n">
         <v>0</v>
       </c>
       <c r="AL117" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AM117" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN117" t="n">
-        <v>6</v>
+        <v>149</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Sulastri Bawenti</t>
+          <t>Stevanus Francois Mangeghong</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>sulastribwnti@gmail.com</t>
+          <t>stivfrancois@gmail.com</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Sutrisno Sariang</t>
+          <t>Fresly Jeica Manangkoda</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>sutrisnosariang90@gmail.com</t>
+          <t>fmanangkoda12@gmail.com</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>(100) TABUKAN UTARA</t>
+          <t>(050) TAMAKO</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>5760</v>
+        <v>3870</v>
       </c>
       <c r="H118" t="n">
         <v>100</v>
       </c>
       <c r="I118" t="n">
-        <v>10.41</v>
+        <v>16.48</v>
       </c>
       <c r="J118" t="n">
-        <v>4610</v>
+        <v>2840</v>
       </c>
       <c r="K118" t="n">
-        <v>453.43</v>
+        <v>485.67</v>
       </c>
       <c r="L118" t="n">
-        <v>134</v>
+        <v>64</v>
       </c>
       <c r="M118" t="n">
-        <v>360</v>
+        <v>320</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -16248,22 +16236,22 @@
         <v>42</v>
       </c>
       <c r="U118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V118" t="n">
-        <v>537</v>
+        <v>435</v>
       </c>
       <c r="W118" t="n">
-        <v>403</v>
+        <v>371</v>
       </c>
       <c r="X118" t="n">
-        <v>134</v>
+        <v>64</v>
       </c>
       <c r="Y118" t="n">
-        <v>360</v>
+        <v>320</v>
       </c>
       <c r="Z118" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA118" t="n">
         <v>0</v>
@@ -16284,84 +16272,84 @@
         <v>42</v>
       </c>
       <c r="AG118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH118" t="n">
-        <v>537</v>
+        <v>435</v>
       </c>
       <c r="AI118" t="n">
-        <v>403</v>
+        <v>371</v>
       </c>
       <c r="AJ118" t="n">
-        <v>378</v>
+        <v>64</v>
       </c>
       <c r="AK118" t="n">
         <v>0</v>
       </c>
       <c r="AL118" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AM118" t="n">
         <v>0</v>
       </c>
       <c r="AN118" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Sunardi Tamado</t>
+          <t>Sulastri Bawenti</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>sunarditamado2@gmail.com</t>
+          <t>sulastribwnti@gmail.com</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Johny Steven Manoppo</t>
+          <t>Sutrisno Sariang</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>stevenmanoppo36@gmail.com</t>
+          <t>sutrisnosariang90@gmail.com</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>(040) MANGANITU SELATAN</t>
+          <t>(100) TABUKAN UTARA</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>5040</v>
+        <v>5760</v>
       </c>
       <c r="H119" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="I119" t="n">
-        <v>6.33</v>
+        <v>10.41</v>
       </c>
       <c r="J119" t="n">
-        <v>4250</v>
+        <v>4610</v>
       </c>
       <c r="K119" t="n">
-        <v>335.3</v>
+        <v>453.43</v>
       </c>
       <c r="L119" t="n">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="M119" t="n">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="N119" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -16373,31 +16361,31 @@
         <v>0</v>
       </c>
       <c r="R119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
       </c>
       <c r="T119" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="U119" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V119" t="n">
-        <v>486</v>
+        <v>537</v>
       </c>
       <c r="W119" t="n">
-        <v>442</v>
+        <v>403</v>
       </c>
       <c r="X119" t="n">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="Y119" t="n">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="Z119" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -16409,93 +16397,93 @@
         <v>0</v>
       </c>
       <c r="AD119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE119" t="n">
         <v>0</v>
       </c>
       <c r="AF119" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="AG119" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AH119" t="n">
-        <v>486</v>
+        <v>537</v>
       </c>
       <c r="AI119" t="n">
-        <v>442</v>
+        <v>403</v>
       </c>
       <c r="AJ119" t="n">
-        <v>420</v>
+        <v>134</v>
       </c>
       <c r="AK119" t="n">
         <v>0</v>
       </c>
       <c r="AL119" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AM119" t="n">
         <v>0</v>
       </c>
       <c r="AN119" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Oktavianti Tangkabiringan</t>
+          <t>Sunardi Tamado</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>tangkabiringananti@gmail.com</t>
+          <t>sunarditamado2@gmail.com</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Hastuti Manabung</t>
+          <t>Johny Steven Manoppo</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>hmanabung01@gmail.com</t>
+          <t>stevenmanoppo36@gmail.com</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>(110) KENDAHE</t>
+          <t>(040) MANGANITU SELATAN</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>3580</v>
+        <v>5040</v>
       </c>
       <c r="H120" t="n">
-        <v>170</v>
+        <v>90</v>
       </c>
       <c r="I120" t="n">
-        <v>13.57</v>
+        <v>6.33</v>
       </c>
       <c r="J120" t="n">
-        <v>2510</v>
+        <v>4250</v>
       </c>
       <c r="K120" t="n">
-        <v>213.88</v>
+        <v>335.3</v>
       </c>
       <c r="L120" t="n">
-        <v>164</v>
+        <v>44</v>
       </c>
       <c r="M120" t="n">
-        <v>266</v>
+        <v>378</v>
       </c>
       <c r="N120" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -16507,31 +16495,31 @@
         <v>0</v>
       </c>
       <c r="R120" t="n">
+        <v>1</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0</v>
+      </c>
+      <c r="T120" t="n">
+        <v>58</v>
+      </c>
+      <c r="U120" t="n">
         <v>3</v>
       </c>
-      <c r="S120" t="n">
-        <v>0</v>
-      </c>
-      <c r="T120" t="n">
-        <v>96</v>
-      </c>
-      <c r="U120" t="n">
-        <v>0</v>
-      </c>
       <c r="V120" t="n">
-        <v>544</v>
+        <v>486</v>
       </c>
       <c r="W120" t="n">
-        <v>380</v>
+        <v>442</v>
       </c>
       <c r="X120" t="n">
-        <v>164</v>
+        <v>44</v>
       </c>
       <c r="Y120" t="n">
-        <v>266</v>
+        <v>378</v>
       </c>
       <c r="Z120" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="AA120" t="n">
         <v>0</v>
@@ -16543,96 +16531,96 @@
         <v>0</v>
       </c>
       <c r="AD120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>58</v>
+      </c>
+      <c r="AG120" t="n">
         <v>3</v>
       </c>
-      <c r="AE120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF120" t="n">
-        <v>96</v>
-      </c>
-      <c r="AG120" t="n">
-        <v>0</v>
-      </c>
       <c r="AH120" t="n">
-        <v>544</v>
+        <v>486</v>
       </c>
       <c r="AI120" t="n">
-        <v>380</v>
+        <v>442</v>
       </c>
       <c r="AJ120" t="n">
-        <v>430</v>
+        <v>44</v>
       </c>
       <c r="AK120" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AL120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM120" t="n">
         <v>0</v>
       </c>
       <c r="AN120" t="n">
-        <v>0</v>
+        <v>378</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Ambrosius Tampi Tangkabiringan</t>
+          <t>Oktavianti Tangkabiringan</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>tangkabiringanayen70@gmail.com</t>
+          <t>tangkabiringananti@gmail.com</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>George Muler Sasiang</t>
+          <t>Hastuti Manabung</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>georgemulersasiangsasiang@gmail.com</t>
+          <t>hmanabung01@gmail.com</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>(090) TAHUNA</t>
+          <t>(110) KENDAHE</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>2220</v>
+        <v>3580</v>
       </c>
       <c r="H121" t="n">
-        <v>1180</v>
+        <v>170</v>
       </c>
       <c r="I121" t="n">
-        <v>110.84</v>
+        <v>13.57</v>
       </c>
       <c r="J121" t="n">
-        <v>810</v>
+        <v>2510</v>
       </c>
       <c r="K121" t="n">
-        <v>147.87</v>
+        <v>213.88</v>
       </c>
       <c r="L121" t="n">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="M121" t="n">
-        <v>242</v>
+        <v>266</v>
       </c>
       <c r="N121" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="O121" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P121" t="n">
         <v>0</v>
@@ -16641,34 +16629,34 @@
         <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
       </c>
       <c r="T121" t="n">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="U121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V121" t="n">
-        <v>479</v>
+        <v>544</v>
       </c>
       <c r="W121" t="n">
-        <v>292</v>
+        <v>380</v>
       </c>
       <c r="X121" t="n">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="Y121" t="n">
-        <v>242</v>
+        <v>266</v>
       </c>
       <c r="Z121" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="AA121" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB121" t="n">
         <v>0</v>
@@ -16677,96 +16665,96 @@
         <v>0</v>
       </c>
       <c r="AD121" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE121" t="n">
         <v>0</v>
       </c>
       <c r="AF121" t="n">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="AG121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH121" t="n">
-        <v>479</v>
+        <v>544</v>
       </c>
       <c r="AI121" t="n">
-        <v>292</v>
+        <v>380</v>
       </c>
       <c r="AJ121" t="n">
-        <v>379</v>
+        <v>164</v>
       </c>
       <c r="AK121" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AL121" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AM121" t="n">
         <v>0</v>
       </c>
       <c r="AN121" t="n">
-        <v>0</v>
+        <v>266</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Muhamad Fadly Djafar</t>
+          <t>Ambrosius Tampi Tangkabiringan</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>tentangsangihe@gmail.com</t>
+          <t>tangkabiringanayen70@gmail.com</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Hastuti Manabung</t>
+          <t>George Muler Sasiang</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>hmanabung01@gmail.com</t>
+          <t>georgemulersasiangsasiang@gmail.com</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>(110) KENDAHE</t>
+          <t>(090) TAHUNA</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>3760</v>
+        <v>2220</v>
       </c>
       <c r="H122" t="n">
-        <v>180</v>
+        <v>1180</v>
       </c>
       <c r="I122" t="n">
-        <v>22.18</v>
+        <v>110.84</v>
       </c>
       <c r="J122" t="n">
-        <v>2740</v>
+        <v>810</v>
       </c>
       <c r="K122" t="n">
-        <v>290.99</v>
+        <v>147.87</v>
       </c>
       <c r="L122" t="n">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="M122" t="n">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="N122" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="O122" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P122" t="n">
         <v>0</v>
@@ -16775,34 +16763,34 @@
         <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
       </c>
       <c r="T122" t="n">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="U122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V122" t="n">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="W122" t="n">
-        <v>359</v>
+        <v>292</v>
       </c>
       <c r="X122" t="n">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="Y122" t="n">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="Z122" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="AA122" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB122" t="n">
         <v>0</v>
@@ -16811,192 +16799,192 @@
         <v>0</v>
       </c>
       <c r="AD122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE122" t="n">
         <v>0</v>
       </c>
       <c r="AF122" t="n">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="AG122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH122" t="n">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="AI122" t="n">
-        <v>359</v>
+        <v>292</v>
       </c>
       <c r="AJ122" t="n">
-        <v>419</v>
+        <v>185</v>
       </c>
       <c r="AK122" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AL122" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AM122" t="n">
         <v>0</v>
       </c>
       <c r="AN122" t="n">
-        <v>0</v>
+        <v>242</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Septian Sulaiman</t>
+          <t>Muhamad Fadly Djafar</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>tianfirnanda16@gmail.com</t>
+          <t>tentangsangihe@gmail.com</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Ivonne Lariunaung</t>
+          <t>Hastuti Manabung</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>vonnelariunaung77560@gmail.com</t>
+          <t>hmanabung01@gmail.com</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>(091) TAHUNA TIMUR</t>
+          <t>(110) KENDAHE</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>2400</v>
+        <v>3760</v>
       </c>
       <c r="H123" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="I123" t="n">
-        <v>42.4</v>
+        <v>22.18</v>
       </c>
       <c r="J123" t="n">
-        <v>1800</v>
+        <v>2740</v>
       </c>
       <c r="K123" t="n">
-        <v>535.58</v>
+        <v>290.99</v>
       </c>
       <c r="L123" t="n">
-        <v>97</v>
+        <v>126</v>
       </c>
       <c r="M123" t="n">
-        <v>338</v>
+        <v>256</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O123" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q123" t="n">
         <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
       </c>
       <c r="T123" t="n">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="U123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V123" t="n">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="W123" t="n">
-        <v>398</v>
+        <v>359</v>
       </c>
       <c r="X123" t="n">
-        <v>97</v>
+        <v>126</v>
       </c>
       <c r="Y123" t="n">
-        <v>338</v>
+        <v>256</v>
       </c>
       <c r="Z123" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AA123" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
       </c>
       <c r="AD123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE123" t="n">
         <v>0</v>
       </c>
       <c r="AF123" t="n">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="AG123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH123" t="n">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="AI123" t="n">
-        <v>398</v>
+        <v>359</v>
       </c>
       <c r="AJ123" t="n">
-        <v>432</v>
+        <v>126</v>
       </c>
       <c r="AK123" t="n">
         <v>0</v>
       </c>
       <c r="AL123" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AM123" t="n">
         <v>0</v>
       </c>
       <c r="AN123" t="n">
-        <v>3</v>
+        <v>256</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Rachmawati Kampi</t>
+          <t>Septian Sulaiman</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>tikamustika1704@gmail.com</t>
+          <t>tianfirnanda16@gmail.com</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Jenie Oktavin Rahmawati Monok</t>
+          <t>Ivonne Lariunaung</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>jeniemonok7@gmail.com</t>
+          <t>vonnelariunaung77560@gmail.com</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -17010,34 +16998,34 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>2980</v>
+        <v>1830</v>
       </c>
       <c r="H124" t="n">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="I124" t="n">
-        <v>32.54</v>
+        <v>70.18000000000001</v>
       </c>
       <c r="J124" t="n">
-        <v>2230</v>
+        <v>1280</v>
       </c>
       <c r="K124" t="n">
-        <v>299.55</v>
+        <v>421.48</v>
       </c>
       <c r="L124" t="n">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="M124" t="n">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="N124" t="n">
         <v>0</v>
       </c>
       <c r="O124" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="P124" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q124" t="n">
         <v>0</v>
@@ -17049,31 +17037,31 @@
         <v>0</v>
       </c>
       <c r="T124" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="U124" t="n">
         <v>1</v>
       </c>
       <c r="V124" t="n">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="W124" t="n">
         <v>371</v>
       </c>
       <c r="X124" t="n">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="Y124" t="n">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="Z124" t="n">
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AB124" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -17085,90 +17073,90 @@
         <v>0</v>
       </c>
       <c r="AF124" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="AG124" t="n">
         <v>1</v>
       </c>
       <c r="AH124" t="n">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="AI124" t="n">
         <v>371</v>
       </c>
       <c r="AJ124" t="n">
-        <v>437</v>
+        <v>128</v>
       </c>
       <c r="AK124" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AL124" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AM124" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AN124" t="n">
-        <v>0</v>
+        <v>332</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Kristia Mirnawati Tumpias</t>
+          <t>Rachmawati Kampi</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>tumpiask@gmail.com</t>
+          <t>tikamustika1704@gmail.com</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Johny Steven Manoppo</t>
+          <t>Jenie Oktavin Rahmawati Monok</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>stevenmanoppo36@gmail.com</t>
+          <t>jeniemonok7@gmail.com</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>(040) MANGANITU SELATAN</t>
+          <t>(091) TAHUNA TIMUR</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>4700</v>
+        <v>2980</v>
       </c>
       <c r="H125" t="n">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="I125" t="n">
-        <v>12.28</v>
+        <v>32.54</v>
       </c>
       <c r="J125" t="n">
-        <v>3610</v>
+        <v>2230</v>
       </c>
       <c r="K125" t="n">
-        <v>232.84</v>
+        <v>299.55</v>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="M125" t="n">
-        <v>288</v>
+        <v>326</v>
       </c>
       <c r="N125" t="n">
         <v>0</v>
       </c>
       <c r="O125" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P125" t="n">
         <v>0</v>
@@ -17177,403 +17165,403 @@
         <v>0</v>
       </c>
       <c r="R125" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0</v>
+      </c>
+      <c r="T125" t="n">
+        <v>44</v>
+      </c>
+      <c r="U125" t="n">
+        <v>1</v>
+      </c>
+      <c r="V125" t="n">
+        <v>514</v>
+      </c>
+      <c r="W125" t="n">
+        <v>371</v>
+      </c>
+      <c r="X125" t="n">
+        <v>141</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>326</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA125" t="n">
         <v>2</v>
       </c>
-      <c r="S125" t="n">
-        <v>1</v>
-      </c>
-      <c r="T125" t="n">
-        <v>79</v>
-      </c>
-      <c r="U125" t="n">
+      <c r="AB125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>44</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>514</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>371</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>141</v>
+      </c>
+      <c r="AK125" t="n">
         <v>2</v>
       </c>
-      <c r="V125" t="n">
-        <v>372</v>
-      </c>
-      <c r="W125" t="n">
-        <v>372</v>
-      </c>
-      <c r="X125" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y125" t="n">
-        <v>288</v>
-      </c>
-      <c r="Z125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD125" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE125" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF125" t="n">
-        <v>79</v>
-      </c>
-      <c r="AG125" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH125" t="n">
-        <v>372</v>
-      </c>
-      <c r="AI125" t="n">
-        <v>372</v>
-      </c>
-      <c r="AJ125" t="n">
-        <v>303</v>
-      </c>
-      <c r="AK125" t="n">
-        <v>0</v>
-      </c>
       <c r="AL125" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AM125" t="n">
         <v>0</v>
       </c>
       <c r="AN125" t="n">
-        <v>0</v>
+        <v>326</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Don Albert Seimahuira</t>
+          <t>Kristia Mirnawati Tumpias</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>ungkealbert39@gmail.com</t>
+          <t>tumpiask@gmail.com</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Ferdinand Tangkabiringan</t>
+          <t>Johny Steven Manoppo</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>ferdinandtangkabiringan@gmail.com</t>
+          <t>stevenmanoppo36@gmail.com</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>(090) TAHUNA</t>
+          <t>(040) MANGANITU SELATAN</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>1620</v>
+        <v>4700</v>
       </c>
       <c r="H126" t="n">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="I126" t="n">
-        <v>57.07</v>
+        <v>12.28</v>
       </c>
       <c r="J126" t="n">
-        <v>1230</v>
+        <v>3610</v>
       </c>
       <c r="K126" t="n">
-        <v>351.51</v>
+        <v>232.84</v>
       </c>
       <c r="L126" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>306</v>
+        <v>288</v>
       </c>
       <c r="N126" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0</v>
+      </c>
+      <c r="R126" t="n">
         <v>2</v>
       </c>
-      <c r="O126" t="n">
-        <v>0</v>
-      </c>
-      <c r="P126" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
-      <c r="R126" t="n">
-        <v>1</v>
-      </c>
       <c r="S126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T126" t="n">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="U126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V126" t="n">
-        <v>441</v>
+        <v>372</v>
       </c>
       <c r="W126" t="n">
-        <v>340</v>
+        <v>372</v>
       </c>
       <c r="X126" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>306</v>
+        <v>288</v>
       </c>
       <c r="Z126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD126" t="n">
         <v>2</v>
       </c>
-      <c r="AA126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD126" t="n">
-        <v>1</v>
-      </c>
       <c r="AE126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF126" t="n">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="AG126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH126" t="n">
-        <v>441</v>
+        <v>372</v>
       </c>
       <c r="AI126" t="n">
-        <v>340</v>
+        <v>372</v>
       </c>
       <c r="AJ126" t="n">
-        <v>366</v>
+        <v>0</v>
       </c>
       <c r="AK126" t="n">
         <v>0</v>
       </c>
       <c r="AL126" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM126" t="n">
         <v>0</v>
       </c>
       <c r="AN126" t="n">
-        <v>0</v>
+        <v>288</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Verawati Cristy Lolaroh</t>
+          <t>Don Albert Seimahuira</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>verawaticristylolaroh02@gmail.com</t>
+          <t>ungkealbert39@gmail.com</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Jenie Oktavin Rahmawati Monok</t>
+          <t>Ferdinand Tangkabiringan</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>jeniemonok7@gmail.com</t>
+          <t>ferdinandtangkabiringan@gmail.com</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>(091) TAHUNA TIMUR</t>
+          <t>(090) TAHUNA</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>2410</v>
+        <v>1620</v>
       </c>
       <c r="H127" t="n">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="I127" t="n">
-        <v>35.91</v>
+        <v>57.07</v>
       </c>
       <c r="J127" t="n">
-        <v>2030</v>
+        <v>1230</v>
       </c>
       <c r="K127" t="n">
-        <v>427.15</v>
+        <v>351.51</v>
       </c>
       <c r="L127" t="n">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="M127" t="n">
-        <v>268</v>
+        <v>306</v>
       </c>
       <c r="N127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O127" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="P127" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q127" t="n">
         <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
       </c>
       <c r="T127" t="n">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="U127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V127" t="n">
-        <v>505</v>
+        <v>441</v>
       </c>
       <c r="W127" t="n">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="X127" t="n">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="Y127" t="n">
-        <v>268</v>
+        <v>306</v>
       </c>
       <c r="Z127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA127" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AB127" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
       </c>
       <c r="AD127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE127" t="n">
         <v>0</v>
       </c>
       <c r="AF127" t="n">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="AG127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH127" t="n">
-        <v>505</v>
+        <v>441</v>
       </c>
       <c r="AI127" t="n">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="AJ127" t="n">
-        <v>394</v>
+        <v>101</v>
       </c>
       <c r="AK127" t="n">
         <v>0</v>
       </c>
       <c r="AL127" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AM127" t="n">
         <v>0</v>
       </c>
       <c r="AN127" t="n">
-        <v>1</v>
+        <v>306</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Erin Fernanda Wenas</t>
+          <t>Verawati Cristy Lolaroh</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>wenaserin@gmail.com</t>
+          <t>verawaticristylolaroh02@gmail.com</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>George Muler Sasiang</t>
+          <t>Jenie Oktavin Rahmawati Monok</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>georgemulersasiangsasiang@gmail.com</t>
+          <t>jeniemonok7@gmail.com</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>(090) TAHUNA</t>
+          <t>(091) TAHUNA TIMUR</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>1530</v>
+        <v>2410</v>
       </c>
       <c r="H128" t="n">
-        <v>290</v>
+        <v>190</v>
       </c>
       <c r="I128" t="n">
-        <v>81</v>
+        <v>35.91</v>
       </c>
       <c r="J128" t="n">
-        <v>950</v>
+        <v>2030</v>
       </c>
       <c r="K128" t="n">
-        <v>232.84</v>
+        <v>427.15</v>
       </c>
       <c r="L128" t="n">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="M128" t="n">
-        <v>317</v>
+        <v>268</v>
       </c>
       <c r="N128" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O128" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="P128" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q128" t="n">
         <v>0</v>
@@ -17585,31 +17573,31 @@
         <v>0</v>
       </c>
       <c r="T128" t="n">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="U128" t="n">
         <v>0</v>
       </c>
       <c r="V128" t="n">
-        <v>481</v>
+        <v>505</v>
       </c>
       <c r="W128" t="n">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="X128" t="n">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="Y128" t="n">
-        <v>317</v>
+        <v>268</v>
       </c>
       <c r="Z128" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AA128" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="AB128" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -17621,93 +17609,93 @@
         <v>0</v>
       </c>
       <c r="AF128" t="n">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="AG128" t="n">
         <v>0</v>
       </c>
       <c r="AH128" t="n">
-        <v>481</v>
+        <v>505</v>
       </c>
       <c r="AI128" t="n">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AJ128" t="n">
-        <v>372</v>
+        <v>142</v>
       </c>
       <c r="AK128" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AL128" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AM128" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AN128" t="n">
-        <v>0</v>
+        <v>268</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Winda Metia</t>
+          <t>Erin Fernanda Wenas</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>windametia67@gmail.com</t>
+          <t>wenaserin@gmail.com</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Jeferson Manahampi</t>
+          <t>George Muler Sasiang</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>manahampijeferson94@gmail.com</t>
+          <t>georgemulersasiangsasiang@gmail.com</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>(040) MANGANITU SELATAN</t>
+          <t>(090) TAHUNA</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>3790</v>
+        <v>1530</v>
       </c>
       <c r="H129" t="n">
-        <v>70</v>
+        <v>290</v>
       </c>
       <c r="I129" t="n">
-        <v>5.62</v>
+        <v>81</v>
       </c>
       <c r="J129" t="n">
-        <v>2570</v>
+        <v>950</v>
       </c>
       <c r="K129" t="n">
-        <v>274.95</v>
+        <v>232.84</v>
       </c>
       <c r="L129" t="n">
-        <v>59</v>
+        <v>131</v>
       </c>
       <c r="M129" t="n">
-        <v>187</v>
+        <v>317</v>
       </c>
       <c r="N129" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="O129" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="P129" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q129" t="n">
         <v>0</v>
@@ -17719,88 +17707,88 @@
         <v>0</v>
       </c>
       <c r="T129" t="n">
-        <v>99</v>
+        <v>13</v>
       </c>
       <c r="U129" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V129" t="n">
-        <v>360</v>
+        <v>481</v>
       </c>
       <c r="W129" t="n">
-        <v>301</v>
+        <v>337</v>
       </c>
       <c r="X129" t="n">
-        <v>59</v>
+        <v>131</v>
       </c>
       <c r="Y129" t="n">
-        <v>189</v>
+        <v>317</v>
       </c>
       <c r="Z129" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AA129" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AB129" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
       </c>
       <c r="AD129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE129" t="n">
         <v>0</v>
       </c>
       <c r="AF129" t="n">
-        <v>99</v>
+        <v>13</v>
       </c>
       <c r="AG129" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH129" t="n">
-        <v>360</v>
+        <v>481</v>
       </c>
       <c r="AI129" t="n">
-        <v>301</v>
+        <v>337</v>
       </c>
       <c r="AJ129" t="n">
-        <v>313</v>
+        <v>131</v>
       </c>
       <c r="AK129" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AL129" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AM129" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AN129" t="n">
-        <v>1</v>
+        <v>317</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Yosua Bawembang</t>
+          <t>Winda Metia</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>ybawembang@gmail.com</t>
+          <t>windametia67@gmail.com</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Johny Steven Manoppo</t>
+          <t>Jeferson Manahampi</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>stevenmanoppo36@gmail.com</t>
+          <t>manahampijeferson94@gmail.com</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -17814,34 +17802,34 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>3910</v>
+        <v>3790</v>
       </c>
       <c r="H130" t="n">
-        <v>460</v>
+        <v>70</v>
       </c>
       <c r="I130" t="n">
-        <v>66.17999999999999</v>
+        <v>5.62</v>
       </c>
       <c r="J130" t="n">
-        <v>2510</v>
+        <v>2570</v>
       </c>
       <c r="K130" t="n">
-        <v>243.26</v>
+        <v>274.95</v>
       </c>
       <c r="L130" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="M130" t="n">
-        <v>307</v>
+        <v>187</v>
       </c>
       <c r="N130" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O130" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="P130" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q130" t="n">
         <v>0</v>
@@ -17853,28 +17841,28 @@
         <v>0</v>
       </c>
       <c r="T130" t="n">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="U130" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V130" t="n">
-        <v>447</v>
+        <v>360</v>
       </c>
       <c r="W130" t="n">
-        <v>334</v>
+        <v>301</v>
       </c>
       <c r="X130" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="Y130" t="n">
-        <v>307</v>
+        <v>189</v>
       </c>
       <c r="Z130" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AA130" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="AB130" t="n">
         <v>0</v>
@@ -17883,96 +17871,96 @@
         <v>0</v>
       </c>
       <c r="AD130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE130" t="n">
         <v>0</v>
       </c>
       <c r="AF130" t="n">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="AG130" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH130" t="n">
-        <v>447</v>
+        <v>360</v>
       </c>
       <c r="AI130" t="n">
-        <v>334</v>
+        <v>301</v>
       </c>
       <c r="AJ130" t="n">
-        <v>386</v>
+        <v>59</v>
       </c>
       <c r="AK130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL130" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="AM130" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AN130" t="n">
-        <v>1</v>
+        <v>187</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Yudhistira Prasetya Tangkabiringan</t>
+          <t>Yosua Bawembang</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>yudhistiratangkabiringan@gmail.com</t>
+          <t>ybawembang@gmail.com</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Ferdinand Tangkabiringan</t>
+          <t>Johny Steven Manoppo</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>ferdinandtangkabiringan@gmail.com</t>
+          <t>stevenmanoppo36@gmail.com</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>(090) TAHUNA</t>
+          <t>(040) MANGANITU SELATAN</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>2320</v>
+        <v>3910</v>
       </c>
       <c r="H131" t="n">
-        <v>90</v>
+        <v>460</v>
       </c>
       <c r="I131" t="n">
-        <v>22.97</v>
+        <v>66.17999999999999</v>
       </c>
       <c r="J131" t="n">
-        <v>1520</v>
+        <v>2510</v>
       </c>
       <c r="K131" t="n">
-        <v>337.27</v>
+        <v>243.26</v>
       </c>
       <c r="L131" t="n">
-        <v>139</v>
+        <v>61</v>
       </c>
       <c r="M131" t="n">
-        <v>209</v>
+        <v>307</v>
       </c>
       <c r="N131" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O131" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="P131" t="n">
         <v>0</v>
@@ -17987,28 +17975,28 @@
         <v>0</v>
       </c>
       <c r="T131" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="U131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V131" t="n">
-        <v>400</v>
+        <v>447</v>
       </c>
       <c r="W131" t="n">
-        <v>261</v>
+        <v>334</v>
       </c>
       <c r="X131" t="n">
-        <v>139</v>
+        <v>61</v>
       </c>
       <c r="Y131" t="n">
-        <v>209</v>
+        <v>307</v>
       </c>
       <c r="Z131" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AA131" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AB131" t="n">
         <v>0</v>
@@ -18023,165 +18011,299 @@
         <v>0</v>
       </c>
       <c r="AF131" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="AG131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH131" t="n">
-        <v>400</v>
+        <v>447</v>
       </c>
       <c r="AI131" t="n">
-        <v>261</v>
+        <v>334</v>
       </c>
       <c r="AJ131" t="n">
-        <v>370</v>
+        <v>61</v>
       </c>
       <c r="AK131" t="n">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="AL131" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM131" t="n">
         <v>0</v>
       </c>
       <c r="AN131" t="n">
-        <v>0</v>
+        <v>307</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
+          <t>Yudhistira Prasetya Tangkabiringan</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>yudhistiratangkabiringan@gmail.com</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Ferdinand Tangkabiringan</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>ferdinandtangkabiringan@gmail.com</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>(090) TAHUNA</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Yetty</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
+        <v>2320</v>
+      </c>
+      <c r="H132" t="n">
+        <v>90</v>
+      </c>
+      <c r="I132" t="n">
+        <v>22.97</v>
+      </c>
+      <c r="J132" t="n">
+        <v>1520</v>
+      </c>
+      <c r="K132" t="n">
+        <v>337.27</v>
+      </c>
+      <c r="L132" t="n">
+        <v>139</v>
+      </c>
+      <c r="M132" t="n">
+        <v>209</v>
+      </c>
+      <c r="N132" t="n">
+        <v>6</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0</v>
+      </c>
+      <c r="T132" t="n">
+        <v>46</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0</v>
+      </c>
+      <c r="V132" t="n">
+        <v>400</v>
+      </c>
+      <c r="W132" t="n">
+        <v>261</v>
+      </c>
+      <c r="X132" t="n">
+        <v>139</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>209</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>46</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>400</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>261</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>139</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>6</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
           <t>Yustin Durian</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
+      <c r="B133" t="inlineStr">
         <is>
           <t>yustindurian@gmail.com</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
+      <c r="C133" t="inlineStr">
         <is>
           <t>Fiane Greti Mansauda</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
+      <c r="D133" t="inlineStr">
         <is>
           <t>fianemansauda89@gmail.com</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
+      <c r="E133" t="inlineStr">
         <is>
           <t>(070) TABUKAN TENGAH</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr">
+      <c r="F133" t="inlineStr">
         <is>
           <t>Kharis</t>
         </is>
       </c>
-      <c r="G132" t="n">
+      <c r="G133" t="n">
         <v>3390</v>
       </c>
-      <c r="H132" t="n">
+      <c r="H133" t="n">
         <v>170</v>
       </c>
-      <c r="I132" t="n">
+      <c r="I133" t="n">
         <v>18.7</v>
       </c>
-      <c r="J132" t="n">
+      <c r="J133" t="n">
         <v>2310</v>
       </c>
-      <c r="K132" t="n">
+      <c r="K133" t="n">
         <v>276.16</v>
       </c>
-      <c r="L132" t="n">
+      <c r="L133" t="n">
         <v>131</v>
       </c>
-      <c r="M132" t="n">
+      <c r="M133" t="n">
         <v>278</v>
       </c>
-      <c r="N132" t="n">
+      <c r="N133" t="n">
         <v>2</v>
       </c>
-      <c r="O132" t="n">
-        <v>0</v>
-      </c>
-      <c r="P132" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
-      <c r="R132" t="n">
-        <v>1</v>
-      </c>
-      <c r="S132" t="n">
-        <v>0</v>
-      </c>
-      <c r="T132" t="n">
+      <c r="O133" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0</v>
+      </c>
+      <c r="R133" t="n">
+        <v>1</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0</v>
+      </c>
+      <c r="T133" t="n">
         <v>43</v>
       </c>
-      <c r="U132" t="n">
-        <v>1</v>
-      </c>
-      <c r="V132" t="n">
+      <c r="U133" t="n">
+        <v>1</v>
+      </c>
+      <c r="V133" t="n">
         <v>456</v>
       </c>
-      <c r="W132" t="n">
+      <c r="W133" t="n">
         <v>325</v>
       </c>
-      <c r="X132" t="n">
+      <c r="X133" t="n">
         <v>131</v>
       </c>
-      <c r="Y132" t="n">
+      <c r="Y133" t="n">
         <v>278</v>
       </c>
-      <c r="Z132" t="n">
+      <c r="Z133" t="n">
         <v>2</v>
       </c>
-      <c r="AA132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD132" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF132" t="n">
+      <c r="AA133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF133" t="n">
         <v>43</v>
       </c>
-      <c r="AG132" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH132" t="n">
+      <c r="AG133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH133" t="n">
         <v>456</v>
       </c>
-      <c r="AI132" t="n">
+      <c r="AI133" t="n">
         <v>325</v>
       </c>
-      <c r="AJ132" t="n">
-        <v>368</v>
-      </c>
-      <c r="AK132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL132" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN132" t="n">
-        <v>0</v>
+      <c r="AJ133" t="n">
+        <v>131</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>278</v>
       </c>
     </row>
   </sheetData>
